--- a/dados/LAIA.xlsx
+++ b/dados/LAIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samuel.camargo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2477C20-5E44-4BDA-9593-D8A297136FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA3049E-43B8-4CAE-8CB1-D6B514F10CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2919,6 +2919,21 @@
     <xf numFmtId="0" fontId="57" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="52" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="41" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2943,42 +2958,6 @@
     <xf numFmtId="0" fontId="48" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2996,6 +2975,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3042,19 +3024,37 @@
     <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="14" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21690,7 +21690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A4741E-2134-4562-B632-CA537B03EF9D}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AC157"/>
@@ -21723,13 +21723,13 @@
     <row r="1" spans="1:28" ht="78.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="33"/>
       <c r="B1" s="45"/>
-      <c r="C1" s="104" t="s">
+      <c r="C1" s="109" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
       <c r="J1" s="38"/>
@@ -21754,40 +21754,40 @@
     </row>
     <row r="2" spans="1:28" s="47" customFormat="1" ht="234.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="46"/>
-      <c r="B2" s="105" t="s">
+      <c r="B2" s="110" t="s">
         <v>336</v>
       </c>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="106"/>
-      <c r="F2" s="106"/>
-      <c r="G2" s="106"/>
-      <c r="H2" s="106"/>
-      <c r="I2" s="106"/>
-      <c r="J2" s="106"/>
-      <c r="K2" s="106"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="107"/>
-      <c r="R2" s="108" t="s">
+      <c r="C2" s="111"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="113" t="s">
         <v>335</v>
       </c>
-      <c r="S2" s="108"/>
-      <c r="T2" s="111" t="s">
+      <c r="S2" s="113"/>
+      <c r="T2" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
       <c r="W2" s="63"/>
       <c r="X2" s="63"/>
       <c r="Y2" s="63"/>
-      <c r="Z2" s="109" t="s">
+      <c r="Z2" s="114" t="s">
         <v>261</v>
       </c>
-      <c r="AA2" s="110"/>
+      <c r="AA2" s="115"/>
       <c r="AB2" s="98"/>
     </row>
     <row r="3" spans="1:28" s="49" customFormat="1" ht="401" customHeight="1" x14ac:dyDescent="1.1000000000000001">
@@ -21876,7 +21876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:28" s="52" customFormat="1" ht="382.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28" s="52" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="50">
         <v>2</v>
       </c>
@@ -21933,7 +21933,7 @@
         <v>60</v>
       </c>
       <c r="S4" s="75" t="str">
-        <f>IF(R4&gt;400,"Insustentável (risco extremo)", IF(R4&gt;200,"Significativo (risco muito alto)", IF(R4&gt;70,"Significativo (alto risco)", IF(R4&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="S4:S35" si="0">IF(R4&gt;400,"Insustentável (risco extremo)", IF(R4&gt;200,"Significativo (risco muito alto)", IF(R4&gt;70,"Significativo (alto risco)", IF(R4&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T4" s="67" t="s">
@@ -21955,18 +21955,18 @@
         <v>0.5</v>
       </c>
       <c r="Z4" s="77">
-        <f>PRODUCT(W4:Y4)</f>
+        <f t="shared" ref="Z4:Z16" si="1">PRODUCT(W4:Y4)</f>
         <v>4.5</v>
       </c>
       <c r="AA4" s="75" t="str">
-        <f>IF(Z4&gt;400,"Insustentável (risco extremo)", IF(Z4&gt;200,"Significativo (risco muito alto)", IF(Z4&gt;70,"Significativo (alto risco)", IF(Z4&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="AA4:AA35" si="2">IF(Z4&gt;400,"Insustentável (risco extremo)", IF(Z4&gt;200,"Significativo (risco muito alto)", IF(Z4&gt;70,"Significativo (alto risco)", IF(Z4&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="AB4" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:28" s="52" customFormat="1" ht="382.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28" s="52" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="50">
         <v>3</v>
       </c>
@@ -22023,7 +22023,7 @@
         <v>3</v>
       </c>
       <c r="S5" s="75" t="str">
-        <f>IF(R5&gt;400,"Insustentável (risco extremo)", IF(R5&gt;200,"Significativo (risco muito alto)", IF(R5&gt;70,"Significativo (alto risco)", IF(R5&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T5" s="67" t="s">
@@ -22045,18 +22045,18 @@
         <v>0.5</v>
       </c>
       <c r="Z5" s="77">
-        <f>PRODUCT(W5:Y5)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="AA5" s="75" t="str">
-        <f>IF(Z5&gt;400,"Insustentável (risco extremo)", IF(Z5&gt;200,"Significativo (risco muito alto)", IF(Z5&gt;70,"Significativo (alto risco)", IF(Z5&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB5" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="52" customFormat="1" ht="382.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28" s="52" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="50">
         <v>4</v>
       </c>
@@ -22113,7 +22113,7 @@
         <v>40</v>
       </c>
       <c r="S6" s="75" t="str">
-        <f>IF(R6&gt;400,"Insustentável (risco extremo)", IF(R6&gt;200,"Significativo (risco muito alto)", IF(R6&gt;70,"Significativo (alto risco)", IF(R6&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T6" s="80" t="s">
@@ -22135,18 +22135,18 @@
         <v>0.5</v>
       </c>
       <c r="Z6" s="77">
-        <f>PRODUCT(W6:Y6)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="AA6" s="75" t="str">
-        <f>IF(Z6&gt;400,"Insustentável (risco extremo)", IF(Z6&gt;200,"Significativo (risco muito alto)", IF(Z6&gt;70,"Significativo (alto risco)", IF(Z6&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB6" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="52" customFormat="1" ht="382.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28" s="52" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="50">
         <v>5</v>
       </c>
@@ -22202,7 +22202,7 @@
         <v>30</v>
       </c>
       <c r="S7" s="75" t="str">
-        <f>IF(R7&gt;400,"Insustentável (risco extremo)", IF(R7&gt;200,"Significativo (risco muito alto)", IF(R7&gt;70,"Significativo (alto risco)", IF(R7&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T7" s="67" t="s">
@@ -22224,18 +22224,18 @@
         <v>0.5</v>
       </c>
       <c r="Z7" s="77">
-        <f>PRODUCT(W7:Y7)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AA7" s="75" t="str">
-        <f>IF(Z7&gt;400,"Insustentável (risco extremo)", IF(Z7&gt;200,"Significativo (risco muito alto)", IF(Z7&gt;70,"Significativo (alto risco)", IF(Z7&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB7" s="80" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="52" customFormat="1" ht="382.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28" s="52" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="50">
         <v>7</v>
       </c>
@@ -22292,7 +22292,7 @@
         <v>15</v>
       </c>
       <c r="S8" s="75" t="str">
-        <f>IF(R8&gt;400,"Insustentável (risco extremo)", IF(R8&gt;200,"Significativo (risco muito alto)", IF(R8&gt;70,"Significativo (alto risco)", IF(R8&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T8" s="67" t="s">
@@ -22314,18 +22314,18 @@
         <v>0.5</v>
       </c>
       <c r="Z8" s="77">
-        <f>PRODUCT(W8:Y8)</f>
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
       <c r="AA8" s="75" t="str">
-        <f>IF(Z8&gt;400,"Insustentável (risco extremo)", IF(Z8&gt;200,"Significativo (risco muito alto)", IF(Z8&gt;70,"Significativo (alto risco)", IF(Z8&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB8" s="67" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="9" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A9" s="50">
         <v>9</v>
       </c>
@@ -22382,7 +22382,7 @@
         <v>120</v>
       </c>
       <c r="S9" s="75" t="str">
-        <f>IF(R9&gt;400,"Insustentável (risco extremo)", IF(R9&gt;200,"Significativo (risco muito alto)", IF(R9&gt;70,"Significativo (alto risco)", IF(R9&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T9" s="67" t="s">
@@ -22404,18 +22404,18 @@
         <v>1</v>
       </c>
       <c r="Z9" s="77">
-        <f>PRODUCT(W9:Y9)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="AA9" s="75" t="str">
-        <f>IF(Z9&gt;400,"Insustentável (risco extremo)", IF(Z9&gt;200,"Significativo (risco muito alto)", IF(Z9&gt;70,"Significativo (alto risco)", IF(Z9&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB9" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="10" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A10" s="50">
         <v>10</v>
       </c>
@@ -22472,7 +22472,7 @@
         <v>21</v>
       </c>
       <c r="S10" s="75" t="str">
-        <f>IF(R10&gt;400,"Insustentável (risco extremo)", IF(R10&gt;200,"Significativo (risco muito alto)", IF(R10&gt;70,"Significativo (alto risco)", IF(R10&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T10" s="67" t="s">
@@ -22494,18 +22494,18 @@
         <v>0.2</v>
       </c>
       <c r="Z10" s="77">
-        <f>PRODUCT(W10:Y10)</f>
+        <f t="shared" si="1"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA10" s="75" t="str">
-        <f>IF(Z10&gt;400,"Insustentável (risco extremo)", IF(Z10&gt;200,"Significativo (risco muito alto)", IF(Z10&gt;70,"Significativo (alto risco)", IF(Z10&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB10" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="11" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A11" s="50">
         <v>12</v>
       </c>
@@ -22562,7 +22562,7 @@
         <v>45</v>
       </c>
       <c r="S11" s="75" t="str">
-        <f>IF(R11&gt;400,"Insustentável (risco extremo)", IF(R11&gt;200,"Significativo (risco muito alto)", IF(R11&gt;70,"Significativo (alto risco)", IF(R11&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T11" s="67" t="s">
@@ -22584,18 +22584,18 @@
         <v>0.5</v>
       </c>
       <c r="Z11" s="77">
-        <f>PRODUCT(W11:Y11)</f>
+        <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
       <c r="AA11" s="75" t="str">
-        <f>IF(Z11&gt;400,"Insustentável (risco extremo)", IF(Z11&gt;200,"Significativo (risco muito alto)", IF(Z11&gt;70,"Significativo (alto risco)", IF(Z11&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB11" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="12" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A12" s="50">
         <v>13</v>
       </c>
@@ -22651,7 +22651,7 @@
         <v>6</v>
       </c>
       <c r="S12" s="75" t="str">
-        <f>IF(R12&gt;400,"Insustentável (risco extremo)", IF(R12&gt;200,"Significativo (risco muito alto)", IF(R12&gt;70,"Significativo (alto risco)", IF(R12&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T12" s="80" t="s">
@@ -22673,18 +22673,18 @@
         <v>0.1</v>
       </c>
       <c r="Z12" s="77">
-        <f>PRODUCT(W12:Y12)</f>
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
       <c r="AA12" s="75" t="str">
-        <f>IF(Z12&gt;400,"Insustentável (risco extremo)", IF(Z12&gt;200,"Significativo (risco muito alto)", IF(Z12&gt;70,"Significativo (alto risco)", IF(Z12&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB12" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="13" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A13" s="50">
         <v>14</v>
       </c>
@@ -22741,7 +22741,7 @@
         <v>16</v>
       </c>
       <c r="S13" s="75" t="str">
-        <f>IF(R13&gt;400,"Insustentável (risco extremo)", IF(R13&gt;200,"Significativo (risco muito alto)", IF(R13&gt;70,"Significativo (alto risco)", IF(R13&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T13" s="67" t="s">
@@ -22763,18 +22763,18 @@
         <v>0.1</v>
       </c>
       <c r="Z13" s="77">
-        <f>PRODUCT(W13:Y13)</f>
+        <f t="shared" si="1"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA13" s="75" t="str">
-        <f>IF(Z13&gt;400,"Insustentável (risco extremo)", IF(Z13&gt;200,"Significativo (risco muito alto)", IF(Z13&gt;70,"Significativo (alto risco)", IF(Z13&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB13" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="14" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A14" s="50">
         <v>15</v>
       </c>
@@ -22831,7 +22831,7 @@
         <v>9</v>
       </c>
       <c r="S14" s="75" t="str">
-        <f>IF(R14&gt;400,"Insustentável (risco extremo)", IF(R14&gt;200,"Significativo (risco muito alto)", IF(R14&gt;70,"Significativo (alto risco)", IF(R14&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T14" s="67" t="s">
@@ -22853,18 +22853,18 @@
         <v>0.1</v>
       </c>
       <c r="Z14" s="77">
-        <f>PRODUCT(W14:Y14)</f>
+        <f t="shared" si="1"/>
         <v>1.8</v>
       </c>
       <c r="AA14" s="75" t="str">
-        <f>IF(Z14&gt;400,"Insustentável (risco extremo)", IF(Z14&gt;200,"Significativo (risco muito alto)", IF(Z14&gt;70,"Significativo (alto risco)", IF(Z14&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB14" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="15" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A15" s="50">
         <v>16</v>
       </c>
@@ -22921,7 +22921,7 @@
         <v>6</v>
       </c>
       <c r="S15" s="75" t="str">
-        <f>IF(R15&gt;400,"Insustentável (risco extremo)", IF(R15&gt;200,"Significativo (risco muito alto)", IF(R15&gt;70,"Significativo (alto risco)", IF(R15&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T15" s="67" t="s">
@@ -22943,18 +22943,18 @@
         <v>0.2</v>
       </c>
       <c r="Z15" s="77">
-        <f>PRODUCT(W15:Y15)</f>
+        <f t="shared" si="1"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA15" s="75" t="str">
-        <f>IF(Z15&gt;400,"Insustentável (risco extremo)", IF(Z15&gt;200,"Significativo (risco muito alto)", IF(Z15&gt;70,"Significativo (alto risco)", IF(Z15&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB15" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="16" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A16" s="50">
         <v>17</v>
       </c>
@@ -23011,7 +23011,7 @@
         <v>9</v>
       </c>
       <c r="S16" s="75" t="str">
-        <f>IF(R16&gt;400,"Insustentável (risco extremo)", IF(R16&gt;200,"Significativo (risco muito alto)", IF(R16&gt;70,"Significativo (alto risco)", IF(R16&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T16" s="67" t="s">
@@ -23033,18 +23033,18 @@
         <v>0.2</v>
       </c>
       <c r="Z16" s="77">
-        <f>PRODUCT(W16:Y16)</f>
+        <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
       <c r="AA16" s="75" t="str">
-        <f>IF(Z16&gt;400,"Insustentável (risco extremo)", IF(Z16&gt;200,"Significativo (risco muito alto)", IF(Z16&gt;70,"Significativo (alto risco)", IF(Z16&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB16" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="17" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A17" s="51">
         <v>20</v>
       </c>
@@ -23100,7 +23100,7 @@
         <v>6</v>
       </c>
       <c r="S17" s="75" t="str">
-        <f>IF(R17&gt;400,"Insustentável (risco extremo)", IF(R17&gt;200,"Significativo (risco muito alto)", IF(R17&gt;70,"Significativo (alto risco)", IF(R17&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T17" s="80" t="s">
@@ -23125,14 +23125,14 @@
         <v>1.8</v>
       </c>
       <c r="AA17" s="75" t="str">
-        <f>IF(Z17&gt;400,"Insustentável (risco extremo)", IF(Z17&gt;200,"Significativo (risco muito alto)", IF(Z17&gt;70,"Significativo (alto risco)", IF(Z17&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB17" s="80" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="18" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A18" s="50">
         <v>21</v>
       </c>
@@ -23185,11 +23185,11 @@
         <v>0.1</v>
       </c>
       <c r="R18" s="74">
-        <f>PRODUCT(O18:Q18)</f>
+        <f t="shared" ref="R18:R59" si="3">PRODUCT(O18:Q18)</f>
         <v>1.5</v>
       </c>
       <c r="S18" s="75" t="str">
-        <f>IF(R18&gt;400,"Insustentável (risco extremo)", IF(R18&gt;200,"Significativo (risco muito alto)", IF(R18&gt;70,"Significativo (alto risco)", IF(R18&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T18" s="67" t="s">
@@ -23211,11 +23211,11 @@
         <v>0.1</v>
       </c>
       <c r="Z18" s="77">
-        <f>PRODUCT(W18:Y18)</f>
+        <f t="shared" ref="Z18:Z59" si="4">PRODUCT(W18:Y18)</f>
         <v>0.70000000000000007</v>
       </c>
       <c r="AA18" s="75" t="str">
-        <f>IF(Z18&gt;400,"Insustentável (risco extremo)", IF(Z18&gt;200,"Significativo (risco muito alto)", IF(Z18&gt;70,"Significativo (alto risco)", IF(Z18&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB18" s="67" t="s">
@@ -23223,7 +23223,7 @@
       </c>
       <c r="AC18" s="55"/>
     </row>
-    <row r="19" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="19" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A19" s="50">
         <v>23</v>
       </c>
@@ -23276,11 +23276,11 @@
         <v>0.5</v>
       </c>
       <c r="R19" s="74">
-        <f>PRODUCT(O19:Q19)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="S19" s="75" t="str">
-        <f>IF(R19&gt;400,"Insustentável (risco extremo)", IF(R19&gt;200,"Significativo (risco muito alto)", IF(R19&gt;70,"Significativo (alto risco)", IF(R19&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T19" s="67" t="s">
@@ -23302,11 +23302,11 @@
         <v>0.1</v>
       </c>
       <c r="Z19" s="77">
-        <f>PRODUCT(W19:Y19)</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA19" s="75" t="str">
-        <f>IF(Z19&gt;400,"Insustentável (risco extremo)", IF(Z19&gt;200,"Significativo (risco muito alto)", IF(Z19&gt;70,"Significativo (alto risco)", IF(Z19&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB19" s="80" t="s">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="AC19" s="55"/>
     </row>
-    <row r="20" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="20" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A20" s="50">
         <v>25</v>
       </c>
@@ -23367,11 +23367,11 @@
         <v>0.5</v>
       </c>
       <c r="R20" s="74">
-        <f>PRODUCT(O20:Q20)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="S20" s="75" t="str">
-        <f>IF(R20&gt;400,"Insustentável (risco extremo)", IF(R20&gt;200,"Significativo (risco muito alto)", IF(R20&gt;70,"Significativo (alto risco)", IF(R20&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T20" s="67" t="s">
@@ -23393,11 +23393,11 @@
         <v>0.2</v>
       </c>
       <c r="Z20" s="77">
-        <f>PRODUCT(W20:Y20)</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA20" s="75" t="str">
-        <f>IF(Z20&gt;400,"Insustentável (risco extremo)", IF(Z20&gt;200,"Significativo (risco muito alto)", IF(Z20&gt;70,"Significativo (alto risco)", IF(Z20&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB20" s="67" t="s">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="AC20" s="55"/>
     </row>
-    <row r="21" spans="1:29" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="21" spans="1:29" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A21" s="50">
         <v>26</v>
       </c>
@@ -23458,11 +23458,11 @@
         <v>0.5</v>
       </c>
       <c r="R21" s="74">
-        <f>PRODUCT(O21:Q21)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="S21" s="75" t="str">
-        <f>IF(R21&gt;400,"Insustentável (risco extremo)", IF(R21&gt;200,"Significativo (risco muito alto)", IF(R21&gt;70,"Significativo (alto risco)", IF(R21&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T21" s="67" t="s">
@@ -23484,11 +23484,11 @@
         <v>0.2</v>
       </c>
       <c r="Z21" s="77">
-        <f>PRODUCT(W21:Y21)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AA21" s="75" t="str">
-        <f>IF(Z21&gt;400,"Insustentável (risco extremo)", IF(Z21&gt;200,"Significativo (risco muito alto)", IF(Z21&gt;70,"Significativo (alto risco)", IF(Z21&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB21" s="67" t="s">
@@ -23496,7 +23496,7 @@
       </c>
       <c r="AC21" s="55"/>
     </row>
-    <row r="22" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="22" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A22" s="50">
         <v>27</v>
       </c>
@@ -23549,11 +23549,11 @@
         <v>0.5</v>
       </c>
       <c r="R22" s="74">
-        <f>PRODUCT(O22:Q22)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S22" s="75" t="str">
-        <f>IF(R22&gt;400,"Insustentável (risco extremo)", IF(R22&gt;200,"Significativo (risco muito alto)", IF(R22&gt;70,"Significativo (alto risco)", IF(R22&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T22" s="67" t="s">
@@ -23575,11 +23575,11 @@
         <v>0.2</v>
       </c>
       <c r="Z22" s="77">
-        <f>PRODUCT(W22:Y22)</f>
+        <f t="shared" si="4"/>
         <v>3.6</v>
       </c>
       <c r="AA22" s="75" t="str">
-        <f>IF(Z22&gt;400,"Insustentável (risco extremo)", IF(Z22&gt;200,"Significativo (risco muito alto)", IF(Z22&gt;70,"Significativo (alto risco)", IF(Z22&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB22" s="67" t="s">
@@ -23587,7 +23587,7 @@
       </c>
       <c r="AC22" s="55"/>
     </row>
-    <row r="23" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="23" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A23" s="50">
         <v>28</v>
       </c>
@@ -23640,11 +23640,11 @@
         <v>0.5</v>
       </c>
       <c r="R23" s="74">
-        <f>PRODUCT(O23:Q23)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S23" s="75" t="str">
-        <f>IF(R23&gt;400,"Insustentável (risco extremo)", IF(R23&gt;200,"Significativo (risco muito alto)", IF(R23&gt;70,"Significativo (alto risco)", IF(R23&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T23" s="67" t="s">
@@ -23666,18 +23666,18 @@
         <v>0.2</v>
       </c>
       <c r="Z23" s="77">
-        <f>PRODUCT(W23:Y23)</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA23" s="75" t="str">
-        <f>IF(Z23&gt;400,"Insustentável (risco extremo)", IF(Z23&gt;200,"Significativo (risco muito alto)", IF(Z23&gt;70,"Significativo (alto risco)", IF(Z23&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB23" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="24" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A24" s="50"/>
       <c r="B24" s="78" t="s">
         <v>26</v>
@@ -23728,11 +23728,11 @@
         <v>3</v>
       </c>
       <c r="R24" s="74">
-        <f>PRODUCT(O24:Q24)</f>
+        <f t="shared" si="3"/>
         <v>270</v>
       </c>
       <c r="S24" s="75" t="str">
-        <f>IF(R24&gt;400,"Insustentável (risco extremo)", IF(R24&gt;200,"Significativo (risco muito alto)", IF(R24&gt;70,"Significativo (alto risco)", IF(R24&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco muito alto)</v>
       </c>
       <c r="T24" s="67" t="s">
@@ -23754,18 +23754,18 @@
         <v>0.5</v>
       </c>
       <c r="Z24" s="77">
-        <f>PRODUCT(W24:Y24)</f>
+        <f t="shared" si="4"/>
         <v>21</v>
       </c>
       <c r="AA24" s="75" t="str">
-        <f>IF(Z24&gt;400,"Insustentável (risco extremo)", IF(Z24&gt;200,"Significativo (risco muito alto)", IF(Z24&gt;70,"Significativo (alto risco)", IF(Z24&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB24" s="67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="25" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A25" s="50">
         <v>29</v>
       </c>
@@ -23818,11 +23818,11 @@
         <v>0.5</v>
       </c>
       <c r="R25" s="74">
-        <f>PRODUCT(O25:Q25)</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="S25" s="75" t="str">
-        <f>IF(R25&gt;400,"Insustentável (risco extremo)", IF(R25&gt;200,"Significativo (risco muito alto)", IF(R25&gt;70,"Significativo (alto risco)", IF(R25&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T25" s="67" t="s">
@@ -23844,18 +23844,18 @@
         <v>0.1</v>
       </c>
       <c r="Z25" s="77">
-        <f>PRODUCT(W25:Y25)</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AA25" s="75" t="str">
-        <f>IF(Z25&gt;400,"Insustentável (risco extremo)", IF(Z25&gt;200,"Significativo (risco muito alto)", IF(Z25&gt;70,"Significativo (alto risco)", IF(Z25&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB25" s="67" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="26" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A26" s="50">
         <v>30</v>
       </c>
@@ -23908,11 +23908,11 @@
         <v>1</v>
       </c>
       <c r="R26" s="74">
-        <f>PRODUCT(O26:Q26)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S26" s="75" t="str">
-        <f>IF(R26&gt;400,"Insustentável (risco extremo)", IF(R26&gt;200,"Significativo (risco muito alto)", IF(R26&gt;70,"Significativo (alto risco)", IF(R26&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T26" s="67" t="s">
@@ -23934,18 +23934,18 @@
         <v>1</v>
       </c>
       <c r="Z26" s="77">
-        <f>PRODUCT(W26:Y26)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA26" s="75" t="str">
-        <f>IF(Z26&gt;400,"Insustentável (risco extremo)", IF(Z26&gt;200,"Significativo (risco muito alto)", IF(Z26&gt;70,"Significativo (alto risco)", IF(Z26&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB26" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="27" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="27" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A27" s="50">
         <v>31</v>
       </c>
@@ -23998,11 +23998,11 @@
         <v>0.5</v>
       </c>
       <c r="R27" s="74">
-        <f>PRODUCT(O27:Q27)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S27" s="75" t="str">
-        <f>IF(R27&gt;400,"Insustentável (risco extremo)", IF(R27&gt;200,"Significativo (risco muito alto)", IF(R27&gt;70,"Significativo (alto risco)", IF(R27&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T27" s="67" t="s">
@@ -24024,18 +24024,18 @@
         <v>0.1</v>
       </c>
       <c r="Z27" s="77">
-        <f>PRODUCT(W27:Y27)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="AA27" s="75" t="str">
-        <f>IF(Z27&gt;400,"Insustentável (risco extremo)", IF(Z27&gt;200,"Significativo (risco muito alto)", IF(Z27&gt;70,"Significativo (alto risco)", IF(Z27&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB27" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="28" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A28" s="50">
         <v>32</v>
       </c>
@@ -24088,11 +24088,11 @@
         <v>0.5</v>
       </c>
       <c r="R28" s="74">
-        <f>PRODUCT(O28:Q28)</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="S28" s="75" t="str">
-        <f>IF(R28&gt;400,"Insustentável (risco extremo)", IF(R28&gt;200,"Significativo (risco muito alto)", IF(R28&gt;70,"Significativo (alto risco)", IF(R28&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T28" s="67" t="s">
@@ -24114,18 +24114,18 @@
         <v>0.5</v>
       </c>
       <c r="Z28" s="77">
-        <f>PRODUCT(W28:Y28)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA28" s="75" t="str">
-        <f>IF(Z28&gt;400,"Insustentável (risco extremo)", IF(Z28&gt;200,"Significativo (risco muito alto)", IF(Z28&gt;70,"Significativo (alto risco)", IF(Z28&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB28" s="67" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="29" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A29" s="50">
         <v>34</v>
       </c>
@@ -24178,11 +24178,11 @@
         <v>3</v>
       </c>
       <c r="R29" s="74">
-        <f>PRODUCT(O29:Q29)</f>
+        <f t="shared" si="3"/>
         <v>90</v>
       </c>
       <c r="S29" s="75" t="str">
-        <f>IF(R29&gt;400,"Insustentável (risco extremo)", IF(R29&gt;200,"Significativo (risco muito alto)", IF(R29&gt;70,"Significativo (alto risco)", IF(R29&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T29" s="67" t="s">
@@ -24204,18 +24204,18 @@
         <v>1</v>
       </c>
       <c r="Z29" s="77">
-        <f>PRODUCT(W29:Y29)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AA29" s="75" t="str">
-        <f>IF(Z29&gt;400,"Insustentável (risco extremo)", IF(Z29&gt;200,"Significativo (risco muito alto)", IF(Z29&gt;70,"Significativo (alto risco)", IF(Z29&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB29" s="67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="30" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A30" s="50">
         <v>35</v>
       </c>
@@ -24268,11 +24268,11 @@
         <v>3</v>
       </c>
       <c r="R30" s="74">
-        <f>PRODUCT(O30:Q30)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="S30" s="75" t="str">
-        <f>IF(R30&gt;400,"Insustentável (risco extremo)", IF(R30&gt;200,"Significativo (risco muito alto)", IF(R30&gt;70,"Significativo (alto risco)", IF(R30&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T30" s="67" t="s">
@@ -24294,18 +24294,18 @@
         <v>0.5</v>
       </c>
       <c r="Z30" s="77">
-        <f>PRODUCT(W30:Y30)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="AA30" s="75" t="str">
-        <f>IF(Z30&gt;400,"Insustentável (risco extremo)", IF(Z30&gt;200,"Significativo (risco muito alto)", IF(Z30&gt;70,"Significativo (alto risco)", IF(Z30&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB30" s="67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="31" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A31" s="50">
         <v>38</v>
       </c>
@@ -24358,11 +24358,11 @@
         <v>1</v>
       </c>
       <c r="R31" s="74">
-        <f>PRODUCT(O31:Q31)</f>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="S31" s="75" t="str">
-        <f>IF(R31&gt;400,"Insustentável (risco extremo)", IF(R31&gt;200,"Significativo (risco muito alto)", IF(R31&gt;70,"Significativo (alto risco)", IF(R31&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T31" s="67" t="s">
@@ -24384,25 +24384,25 @@
         <v>0.5</v>
       </c>
       <c r="Z31" s="77">
-        <f>PRODUCT(W31:Y31)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA31" s="75" t="str">
-        <f>IF(Z31&gt;400,"Insustentável (risco extremo)", IF(Z31&gt;200,"Significativo (risco muito alto)", IF(Z31&gt;70,"Significativo (alto risco)", IF(Z31&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB31" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="32" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A32" s="50">
         <v>39</v>
       </c>
       <c r="B32" s="78" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="149" t="s">
+      <c r="C32" s="108" t="s">
         <v>396</v>
       </c>
       <c r="D32" s="67" t="s">
@@ -24448,11 +24448,11 @@
         <v>3</v>
       </c>
       <c r="R32" s="74">
-        <f>PRODUCT(O32:Q32)</f>
+        <f t="shared" si="3"/>
         <v>45</v>
       </c>
       <c r="S32" s="75" t="str">
-        <f>IF(R32&gt;400,"Insustentável (risco extremo)", IF(R32&gt;200,"Significativo (risco muito alto)", IF(R32&gt;70,"Significativo (alto risco)", IF(R32&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T32" s="67" t="s">
@@ -24474,18 +24474,18 @@
         <v>0.5</v>
       </c>
       <c r="Z32" s="77">
-        <f>PRODUCT(W32:Y32)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="AA32" s="75" t="str">
-        <f>IF(Z32&gt;400,"Insustentável (risco extremo)", IF(Z32&gt;200,"Significativo (risco muito alto)", IF(Z32&gt;70,"Significativo (alto risco)", IF(Z32&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB32" s="67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="33" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A33" s="50">
         <v>43</v>
       </c>
@@ -24538,11 +24538,11 @@
         <v>0.5</v>
       </c>
       <c r="R33" s="74">
-        <f>PRODUCT(O33:Q33)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="S33" s="75" t="str">
-        <f>IF(R33&gt;400,"Insustentável (risco extremo)", IF(R33&gt;200,"Significativo (risco muito alto)", IF(R33&gt;70,"Significativo (alto risco)", IF(R33&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T33" s="67" t="s">
@@ -24564,18 +24564,18 @@
         <v>0.2</v>
       </c>
       <c r="Z33" s="77">
-        <f>PRODUCT(W33:Y33)</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA33" s="75" t="str">
-        <f>IF(Z33&gt;400,"Insustentável (risco extremo)", IF(Z33&gt;200,"Significativo (risco muito alto)", IF(Z33&gt;70,"Significativo (alto risco)", IF(Z33&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
-      <c r="AB33" s="149" t="s">
+      <c r="AB33" s="108" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="34" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="34" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A34" s="50">
         <v>44</v>
       </c>
@@ -24628,11 +24628,11 @@
         <v>1</v>
       </c>
       <c r="R34" s="74">
-        <f>PRODUCT(O34:Q34)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S34" s="75" t="str">
-        <f>IF(R34&gt;400,"Insustentável (risco extremo)", IF(R34&gt;200,"Significativo (risco muito alto)", IF(R34&gt;70,"Significativo (alto risco)", IF(R34&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T34" s="67" t="s">
@@ -24654,18 +24654,18 @@
         <v>0.5</v>
       </c>
       <c r="Z34" s="77">
-        <f>PRODUCT(W34:Y34)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="AA34" s="75" t="str">
-        <f>IF(Z34&gt;400,"Insustentável (risco extremo)", IF(Z34&gt;200,"Significativo (risco muito alto)", IF(Z34&gt;70,"Significativo (alto risco)", IF(Z34&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB34" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="35" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="35" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A35" s="50">
         <v>45</v>
       </c>
@@ -24718,11 +24718,11 @@
         <v>0.5</v>
       </c>
       <c r="R35" s="74">
-        <f>PRODUCT(O35:Q35)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S35" s="75" t="str">
-        <f>IF(R35&gt;400,"Insustentável (risco extremo)", IF(R35&gt;200,"Significativo (risco muito alto)", IF(R35&gt;70,"Significativo (alto risco)", IF(R35&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="0"/>
         <v>Insignificante</v>
       </c>
       <c r="T35" s="67" t="s">
@@ -24744,18 +24744,18 @@
         <v>0.1</v>
       </c>
       <c r="Z35" s="77">
-        <f>PRODUCT(W35:Y35)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA35" s="75" t="str">
-        <f>IF(Z35&gt;400,"Insustentável (risco extremo)", IF(Z35&gt;200,"Significativo (risco muito alto)", IF(Z35&gt;70,"Significativo (alto risco)", IF(Z35&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="2"/>
         <v>Insignificante</v>
       </c>
       <c r="AB35" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="36" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A36" s="50">
         <v>46</v>
       </c>
@@ -24808,11 +24808,11 @@
         <v>3</v>
       </c>
       <c r="R36" s="74">
-        <f>PRODUCT(O36:Q36)</f>
+        <f t="shared" si="3"/>
         <v>270</v>
       </c>
       <c r="S36" s="75" t="str">
-        <f>IF(R36&gt;400,"Insustentável (risco extremo)", IF(R36&gt;200,"Significativo (risco muito alto)", IF(R36&gt;70,"Significativo (alto risco)", IF(R36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="S36:S67" si="5">IF(R36&gt;400,"Insustentável (risco extremo)", IF(R36&gt;200,"Significativo (risco muito alto)", IF(R36&gt;70,"Significativo (alto risco)", IF(R36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Significativo (risco muito alto)</v>
       </c>
       <c r="T36" s="67" t="s">
@@ -24834,18 +24834,18 @@
         <v>3</v>
       </c>
       <c r="Z36" s="77">
-        <f>PRODUCT(W36:Y36)</f>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="AA36" s="75" t="str">
-        <f>IF(Z36&gt;400,"Insustentável (risco extremo)", IF(Z36&gt;200,"Significativo (risco muito alto)", IF(Z36&gt;70,"Significativo (alto risco)", IF(Z36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="AA36:AA67" si="6">IF(Z36&gt;400,"Insustentável (risco extremo)", IF(Z36&gt;200,"Significativo (risco muito alto)", IF(Z36&gt;70,"Significativo (alto risco)", IF(Z36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB36" s="67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="37" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A37" s="50">
         <v>49</v>
       </c>
@@ -24898,11 +24898,11 @@
         <v>0.5</v>
       </c>
       <c r="R37" s="74">
-        <f>PRODUCT(O37:Q37)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="S37" s="75" t="str">
-        <f>IF(R37&gt;400,"Insustentável (risco extremo)", IF(R37&gt;200,"Significativo (risco muito alto)", IF(R37&gt;70,"Significativo (alto risco)", IF(R37&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T37" s="67" t="s">
@@ -24924,18 +24924,18 @@
         <v>0.2</v>
       </c>
       <c r="Z37" s="77">
-        <f>PRODUCT(W37:Y37)</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA37" s="75" t="str">
-        <f>IF(Z37&gt;400,"Insustentável (risco extremo)", IF(Z37&gt;200,"Significativo (risco muito alto)", IF(Z37&gt;70,"Significativo (alto risco)", IF(Z37&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB37" s="67" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="38" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A38" s="57">
         <v>51</v>
       </c>
@@ -24988,11 +24988,11 @@
         <v>0.5</v>
       </c>
       <c r="R38" s="74">
-        <f>PRODUCT(O38:Q38)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S38" s="75" t="str">
-        <f>IF(R38&gt;400,"Insustentável (risco extremo)", IF(R38&gt;200,"Significativo (risco muito alto)", IF(R38&gt;70,"Significativo (alto risco)", IF(R38&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T38" s="67" t="s">
@@ -25014,18 +25014,18 @@
         <v>0.1</v>
       </c>
       <c r="Z38" s="77">
-        <f>PRODUCT(W38:Y38)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="AA38" s="75" t="str">
-        <f>IF(Z38&gt;400,"Insustentável (risco extremo)", IF(Z38&gt;200,"Significativo (risco muito alto)", IF(Z38&gt;70,"Significativo (alto risco)", IF(Z38&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB38" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="39" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="39" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A39" s="57">
         <v>52</v>
       </c>
@@ -25078,11 +25078,11 @@
         <v>0.5</v>
       </c>
       <c r="R39" s="74">
-        <f>PRODUCT(O39:Q39)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S39" s="75" t="str">
-        <f>IF(R39&gt;400,"Insustentável (risco extremo)", IF(R39&gt;200,"Significativo (risco muito alto)", IF(R39&gt;70,"Significativo (alto risco)", IF(R39&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T39" s="67" t="s">
@@ -25104,18 +25104,18 @@
         <v>0.1</v>
       </c>
       <c r="Z39" s="77">
-        <f>PRODUCT(W39:Y39)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA39" s="75" t="str">
-        <f>IF(Z39&gt;400,"Insustentável (risco extremo)", IF(Z39&gt;200,"Significativo (risco muito alto)", IF(Z39&gt;70,"Significativo (alto risco)", IF(Z39&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB39" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="40" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="40" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A40" s="57">
         <v>53</v>
       </c>
@@ -25168,11 +25168,11 @@
         <v>0.5</v>
       </c>
       <c r="R40" s="74">
-        <f>PRODUCT(O40:Q40)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S40" s="75" t="str">
-        <f>IF(R40&gt;400,"Insustentável (risco extremo)", IF(R40&gt;200,"Significativo (risco muito alto)", IF(R40&gt;70,"Significativo (alto risco)", IF(R40&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T40" s="67" t="s">
@@ -25194,18 +25194,18 @@
         <v>0.1</v>
       </c>
       <c r="Z40" s="77">
-        <f>PRODUCT(W40:Y40)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="AA40" s="75" t="str">
-        <f>IF(Z40&gt;400,"Insustentável (risco extremo)", IF(Z40&gt;200,"Significativo (risco muito alto)", IF(Z40&gt;70,"Significativo (alto risco)", IF(Z40&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB40" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="41" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A41" s="57">
         <v>54</v>
       </c>
@@ -25258,11 +25258,11 @@
         <v>0.5</v>
       </c>
       <c r="R41" s="74">
-        <f>PRODUCT(O41:Q41)</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="S41" s="75" t="str">
-        <f>IF(R41&gt;400,"Insustentável (risco extremo)", IF(R41&gt;200,"Significativo (risco muito alto)", IF(R41&gt;70,"Significativo (alto risco)", IF(R41&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T41" s="67" t="s">
@@ -25284,18 +25284,18 @@
         <v>0.5</v>
       </c>
       <c r="Z41" s="77">
-        <f>PRODUCT(W41:Y41)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA41" s="75" t="str">
-        <f>IF(Z41&gt;400,"Insustentável (risco extremo)", IF(Z41&gt;200,"Significativo (risco muito alto)", IF(Z41&gt;70,"Significativo (alto risco)", IF(Z41&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB41" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="42" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A42" s="57">
         <v>55</v>
       </c>
@@ -25348,11 +25348,11 @@
         <v>0.5</v>
       </c>
       <c r="R42" s="74">
-        <f>PRODUCT(O42:Q42)</f>
+        <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
       <c r="S42" s="75" t="str">
-        <f>IF(R42&gt;400,"Insustentável (risco extremo)", IF(R42&gt;200,"Significativo (risco muito alto)", IF(R42&gt;70,"Significativo (alto risco)", IF(R42&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T42" s="67" t="s">
@@ -25374,18 +25374,18 @@
         <v>0.2</v>
       </c>
       <c r="Z42" s="77">
-        <f>PRODUCT(W42:Y42)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="AA42" s="75" t="str">
-        <f>IF(Z42&gt;400,"Insustentável (risco extremo)", IF(Z42&gt;200,"Significativo (risco muito alto)", IF(Z42&gt;70,"Significativo (alto risco)", IF(Z42&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB42" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="43" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A43" s="57">
         <v>56</v>
       </c>
@@ -25438,11 +25438,11 @@
         <v>0.5</v>
       </c>
       <c r="R43" s="74">
-        <f>PRODUCT(O43:Q43)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S43" s="75" t="str">
-        <f>IF(R43&gt;400,"Insustentável (risco extremo)", IF(R43&gt;200,"Significativo (risco muito alto)", IF(R43&gt;70,"Significativo (alto risco)", IF(R43&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T43" s="67" t="s">
@@ -25464,18 +25464,18 @@
         <v>0.1</v>
       </c>
       <c r="Z43" s="77">
-        <f>PRODUCT(W43:Y43)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="AA43" s="75" t="str">
-        <f>IF(Z43&gt;400,"Insustentável (risco extremo)", IF(Z43&gt;200,"Significativo (risco muito alto)", IF(Z43&gt;70,"Significativo (alto risco)", IF(Z43&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB43" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="44" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A44" s="57">
         <v>58</v>
       </c>
@@ -25528,11 +25528,11 @@
         <v>0.5</v>
       </c>
       <c r="R44" s="74">
-        <f>PRODUCT(O44:Q44)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="S44" s="75" t="str">
-        <f>IF(R44&gt;400,"Insustentável (risco extremo)", IF(R44&gt;200,"Significativo (risco muito alto)", IF(R44&gt;70,"Significativo (alto risco)", IF(R44&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T44" s="67" t="s">
@@ -25554,18 +25554,18 @@
         <v>0.2</v>
       </c>
       <c r="Z44" s="77">
-        <f>PRODUCT(W44:Y44)</f>
+        <f t="shared" si="4"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA44" s="75" t="str">
-        <f>IF(Z44&gt;400,"Insustentável (risco extremo)", IF(Z44&gt;200,"Significativo (risco muito alto)", IF(Z44&gt;70,"Significativo (alto risco)", IF(Z44&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB44" s="67" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="45" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="45" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A45" s="57">
         <v>59</v>
       </c>
@@ -25618,11 +25618,11 @@
         <v>0.5</v>
       </c>
       <c r="R45" s="74">
-        <f>PRODUCT(O45:Q45)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="S45" s="75" t="str">
-        <f>IF(R45&gt;400,"Insustentável (risco extremo)", IF(R45&gt;200,"Significativo (risco muito alto)", IF(R45&gt;70,"Significativo (alto risco)", IF(R45&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T45" s="67" t="s">
@@ -25644,22 +25644,22 @@
         <v>0.2</v>
       </c>
       <c r="Z45" s="77">
-        <f>PRODUCT(W45:Y45)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AA45" s="75" t="str">
-        <f>IF(Z45&gt;400,"Insustentável (risco extremo)", IF(Z45&gt;200,"Significativo (risco muito alto)", IF(Z45&gt;70,"Significativo (alto risco)", IF(Z45&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB45" s="67" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="46" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A46" s="50">
         <v>60</v>
       </c>
-      <c r="B46" s="145" t="s">
+      <c r="B46" s="104" t="s">
         <v>26</v>
       </c>
       <c r="C46" s="94" t="s">
@@ -25708,11 +25708,11 @@
         <v>0.5</v>
       </c>
       <c r="R46" s="74">
-        <f>PRODUCT(O46:Q46)</f>
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="S46" s="75" t="str">
-        <f>IF(R46&gt;400,"Insustentável (risco extremo)", IF(R46&gt;200,"Significativo (risco muito alto)", IF(R46&gt;70,"Significativo (alto risco)", IF(R46&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T46" s="80" t="s">
@@ -25734,18 +25734,18 @@
         <v>0.5</v>
       </c>
       <c r="Z46" s="77">
-        <f>PRODUCT(W46:Y46)</f>
+        <f t="shared" si="4"/>
         <v>1.5</v>
       </c>
       <c r="AA46" s="75" t="str">
-        <f>IF(Z46&gt;400,"Insustentável (risco extremo)", IF(Z46&gt;200,"Significativo (risco muito alto)", IF(Z46&gt;70,"Significativo (alto risco)", IF(Z46&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB46" s="80" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="47" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A47" s="50">
         <v>61</v>
       </c>
@@ -25798,11 +25798,11 @@
         <v>0.5</v>
       </c>
       <c r="R47" s="74">
-        <f>PRODUCT(O47:Q47)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S47" s="75" t="str">
-        <f>IF(R47&gt;400,"Insustentável (risco extremo)", IF(R47&gt;200,"Significativo (risco muito alto)", IF(R47&gt;70,"Significativo (alto risco)", IF(R47&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T47" s="80" t="s">
@@ -25824,18 +25824,18 @@
         <v>0.1</v>
       </c>
       <c r="Z47" s="77">
-        <f>PRODUCT(W47:Y47)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA47" s="75" t="str">
-        <f>IF(Z47&gt;400,"Insustentável (risco extremo)", IF(Z47&gt;200,"Significativo (risco muito alto)", IF(Z47&gt;70,"Significativo (alto risco)", IF(Z47&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB47" s="80" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="1:28" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="48" spans="1:28" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A48" s="50">
         <v>62</v>
       </c>
@@ -25888,11 +25888,11 @@
         <v>6</v>
       </c>
       <c r="R48" s="74">
-        <f>PRODUCT(O48:Q48)</f>
+        <f t="shared" si="3"/>
         <v>126</v>
       </c>
       <c r="S48" s="75" t="str">
-        <f>IF(R48&gt;400,"Insustentável (risco extremo)", IF(R48&gt;200,"Significativo (risco muito alto)", IF(R48&gt;70,"Significativo (alto risco)", IF(R48&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T48" s="67" t="s">
@@ -25914,18 +25914,18 @@
         <v>0.1</v>
       </c>
       <c r="Z48" s="77">
-        <f>PRODUCT(W48:Y48)</f>
+        <f t="shared" si="4"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="AA48" s="75" t="str">
-        <f>IF(Z48&gt;400,"Insustentável (risco extremo)", IF(Z48&gt;200,"Significativo (risco muito alto)", IF(Z48&gt;70,"Significativo (alto risco)", IF(Z48&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB48" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="49" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="49" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A49" s="50">
         <v>63</v>
       </c>
@@ -25978,11 +25978,11 @@
         <v>1</v>
       </c>
       <c r="R49" s="74">
-        <f>PRODUCT(O49:Q49)</f>
+        <f t="shared" si="3"/>
         <v>120</v>
       </c>
       <c r="S49" s="75" t="str">
-        <f>IF(R49&gt;400,"Insustentável (risco extremo)", IF(R49&gt;200,"Significativo (risco muito alto)", IF(R49&gt;70,"Significativo (alto risco)", IF(R49&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T49" s="67" t="s">
@@ -26004,18 +26004,18 @@
         <v>1</v>
       </c>
       <c r="Z49" s="77">
-        <f>PRODUCT(W49:Y49)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="AA49" s="75" t="str">
-        <f>IF(Z49&gt;400,"Insustentável (risco extremo)", IF(Z49&gt;200,"Significativo (risco muito alto)", IF(Z49&gt;70,"Significativo (alto risco)", IF(Z49&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB49" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="50" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A50" s="50"/>
       <c r="B50" s="78" t="s">
         <v>26</v>
@@ -26066,11 +26066,11 @@
         <v>0.5</v>
       </c>
       <c r="R50" s="74">
-        <f>PRODUCT(O50:Q50)</f>
+        <f t="shared" si="3"/>
         <v>1.5</v>
       </c>
       <c r="S50" s="75" t="str">
-        <f>IF(R50&gt;400,"Insustentável (risco extremo)", IF(R50&gt;200,"Significativo (risco muito alto)", IF(R50&gt;70,"Significativo (alto risco)", IF(R50&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T50" s="80" t="s">
@@ -26092,18 +26092,18 @@
         <v>0.2</v>
       </c>
       <c r="Z50" s="77">
-        <f>PRODUCT(W50:Y50)</f>
+        <f t="shared" si="4"/>
         <v>0.4</v>
       </c>
       <c r="AA50" s="75" t="str">
-        <f>IF(Z50&gt;400,"Insustentável (risco extremo)", IF(Z50&gt;200,"Significativo (risco muito alto)", IF(Z50&gt;70,"Significativo (alto risco)", IF(Z50&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB50" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="51" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="51" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A51" s="50">
         <v>64</v>
       </c>
@@ -26156,11 +26156,11 @@
         <v>0.1</v>
       </c>
       <c r="R51" s="74">
-        <f>PRODUCT(O51:Q51)</f>
+        <f t="shared" si="3"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="S51" s="75" t="str">
-        <f>IF(R51&gt;400,"Insustentável (risco extremo)", IF(R51&gt;200,"Significativo (risco muito alto)", IF(R51&gt;70,"Significativo (alto risco)", IF(R51&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T51" s="67" t="s">
@@ -26182,18 +26182,18 @@
         <v>0.1</v>
       </c>
       <c r="Z51" s="77">
-        <f>PRODUCT(W51:Y51)</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA51" s="75" t="str">
-        <f>IF(Z51&gt;400,"Insustentável (risco extremo)", IF(Z51&gt;200,"Significativo (risco muito alto)", IF(Z51&gt;70,"Significativo (alto risco)", IF(Z51&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB51" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="52" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A52" s="50">
         <v>66</v>
       </c>
@@ -26246,11 +26246,11 @@
         <v>0.2</v>
       </c>
       <c r="R52" s="74">
-        <f>PRODUCT(O52:Q52)</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="S52" s="75" t="str">
-        <f>IF(R52&gt;400,"Insustentável (risco extremo)", IF(R52&gt;200,"Significativo (risco muito alto)", IF(R52&gt;70,"Significativo (alto risco)", IF(R52&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T52" s="67" t="s">
@@ -26272,18 +26272,18 @@
         <v>1</v>
       </c>
       <c r="Z52" s="77">
-        <f>PRODUCT(W52:Y52)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="AA52" s="75" t="str">
-        <f>IF(Z52&gt;400,"Insustentável (risco extremo)", IF(Z52&gt;200,"Significativo (risco muito alto)", IF(Z52&gt;70,"Significativo (alto risco)", IF(Z52&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB52" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="53" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A53" s="50">
         <v>67</v>
       </c>
@@ -26336,11 +26336,11 @@
         <v>0.5</v>
       </c>
       <c r="R53" s="74">
-        <f>PRODUCT(O53:Q53)</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="S53" s="75" t="str">
-        <f>IF(R53&gt;400,"Insustentável (risco extremo)", IF(R53&gt;200,"Significativo (risco muito alto)", IF(R53&gt;70,"Significativo (alto risco)", IF(R53&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T53" s="67" t="s">
@@ -26362,18 +26362,18 @@
         <v>0.1</v>
       </c>
       <c r="Z53" s="77">
-        <f>PRODUCT(W53:Y53)</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA53" s="75" t="str">
-        <f>IF(Z53&gt;400,"Insustentável (risco extremo)", IF(Z53&gt;200,"Significativo (risco muito alto)", IF(Z53&gt;70,"Significativo (alto risco)", IF(Z53&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB53" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:28" s="54" customFormat="1" ht="382.5" customHeight="1" x14ac:dyDescent="1.45">
+    <row r="54" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" customHeight="1" x14ac:dyDescent="1.45">
       <c r="A54" s="50">
         <v>69</v>
       </c>
@@ -26426,11 +26426,11 @@
         <v>0.2</v>
       </c>
       <c r="R54" s="74">
-        <f>PRODUCT(O54:Q54)</f>
+        <f t="shared" si="3"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="S54" s="75" t="str">
-        <f>IF(R54&gt;400,"Insustentável (risco extremo)", IF(R54&gt;200,"Significativo (risco muito alto)", IF(R54&gt;70,"Significativo (alto risco)", IF(R54&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T54" s="67" t="s">
@@ -26452,18 +26452,18 @@
         <v>0.1</v>
       </c>
       <c r="Z54" s="77">
-        <f>PRODUCT(W54:Y54)</f>
+        <f t="shared" si="4"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA54" s="75" t="str">
-        <f>IF(Z54&gt;400,"Insustentável (risco extremo)", IF(Z54&gt;200,"Significativo (risco muito alto)", IF(Z54&gt;70,"Significativo (alto risco)", IF(Z54&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB54" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="55" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A55" s="50">
         <v>70</v>
       </c>
@@ -26516,11 +26516,11 @@
         <v>0.5</v>
       </c>
       <c r="R55" s="74">
-        <f>PRODUCT(O55:Q55)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="S55" s="75" t="str">
-        <f>IF(R55&gt;400,"Insustentável (risco extremo)", IF(R55&gt;200,"Significativo (risco muito alto)", IF(R55&gt;70,"Significativo (alto risco)", IF(R55&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T55" s="67" t="s">
@@ -26542,18 +26542,18 @@
         <v>0.1</v>
       </c>
       <c r="Z55" s="77">
-        <f>PRODUCT(W55:Y55)</f>
+        <f t="shared" si="4"/>
         <v>1.8</v>
       </c>
       <c r="AA55" s="75" t="str">
-        <f>IF(Z55&gt;400,"Insustentável (risco extremo)", IF(Z55&gt;200,"Significativo (risco muito alto)", IF(Z55&gt;70,"Significativo (alto risco)", IF(Z55&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB55" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="56" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A56" s="50">
         <v>72</v>
       </c>
@@ -26606,11 +26606,11 @@
         <v>0.5</v>
       </c>
       <c r="R56" s="74">
-        <f>PRODUCT(O56:Q56)</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="S56" s="75" t="str">
-        <f>IF(R56&gt;400,"Insustentável (risco extremo)", IF(R56&gt;200,"Significativo (risco muito alto)", IF(R56&gt;70,"Significativo (alto risco)", IF(R56&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T56" s="67" t="s">
@@ -26632,18 +26632,18 @@
         <v>0.2</v>
       </c>
       <c r="Z56" s="77">
-        <f>PRODUCT(W56:Y56)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="AA56" s="75" t="str">
-        <f>IF(Z56&gt;400,"Insustentável (risco extremo)", IF(Z56&gt;200,"Significativo (risco muito alto)", IF(Z56&gt;70,"Significativo (alto risco)", IF(Z56&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB56" s="67" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:28" s="54" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="57" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A57" s="50">
         <v>73</v>
       </c>
@@ -26696,11 +26696,11 @@
         <v>0.2</v>
       </c>
       <c r="R57" s="74">
-        <f>PRODUCT(O57:Q57)</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="S57" s="75" t="str">
-        <f>IF(R57&gt;400,"Insustentável (risco extremo)", IF(R57&gt;200,"Significativo (risco muito alto)", IF(R57&gt;70,"Significativo (alto risco)", IF(R57&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T57" s="67" t="s">
@@ -26722,18 +26722,18 @@
         <v>0.2</v>
       </c>
       <c r="Z57" s="77">
-        <f>PRODUCT(W57:Y57)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AA57" s="75" t="str">
-        <f>IF(Z57&gt;400,"Insustentável (risco extremo)", IF(Z57&gt;200,"Significativo (risco muito alto)", IF(Z57&gt;70,"Significativo (alto risco)", IF(Z57&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB57" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="58" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A58" s="50">
         <v>74</v>
       </c>
@@ -26786,11 +26786,11 @@
         <v>0.5</v>
       </c>
       <c r="R58" s="74">
-        <f>PRODUCT(O58:Q58)</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="S58" s="75" t="str">
-        <f>IF(R58&gt;400,"Insustentável (risco extremo)", IF(R58&gt;200,"Significativo (risco muito alto)", IF(R58&gt;70,"Significativo (alto risco)", IF(R58&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T58" s="90" t="s">
@@ -26812,18 +26812,18 @@
         <v>0.2</v>
       </c>
       <c r="Z58" s="77">
-        <f>PRODUCT(W58:Y58)</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="AA58" s="75" t="str">
-        <f>IF(Z58&gt;400,"Insustentável (risco extremo)", IF(Z58&gt;200,"Significativo (risco muito alto)", IF(Z58&gt;70,"Significativo (alto risco)", IF(Z58&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB58" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="59" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A59" s="50">
         <v>75</v>
       </c>
@@ -26876,11 +26876,11 @@
         <v>0.1</v>
       </c>
       <c r="R59" s="74">
-        <f>PRODUCT(O59:Q59)</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="S59" s="75" t="str">
-        <f>IF(R59&gt;400,"Insustentável (risco extremo)", IF(R59&gt;200,"Significativo (risco muito alto)", IF(R59&gt;70,"Significativo (alto risco)", IF(R59&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="5"/>
         <v>Insignificante</v>
       </c>
       <c r="T59" s="67" t="s">
@@ -26902,18 +26902,18 @@
         <v>0.1</v>
       </c>
       <c r="Z59" s="77">
-        <f>PRODUCT(W59:Y59)</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="AA59" s="75" t="str">
-        <f>IF(Z59&gt;400,"Insustentável (risco extremo)", IF(Z59&gt;200,"Significativo (risco muito alto)", IF(Z59&gt;70,"Significativo (alto risco)", IF(Z59&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="6"/>
         <v>Insignificante</v>
       </c>
       <c r="AB59" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="60" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A60" s="50">
         <v>76</v>
       </c>
@@ -26999,7 +26999,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="61" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A61" s="50">
         <v>77</v>
       </c>
@@ -27052,11 +27052,11 @@
         <v>0.2</v>
       </c>
       <c r="R61" s="74">
-        <f>PRODUCT(O61:Q61)</f>
+        <f t="shared" ref="R61:R92" si="7">PRODUCT(O61:Q61)</f>
         <v>3.6</v>
       </c>
       <c r="S61" s="75" t="str">
-        <f>IF(R61&gt;400,"Insustentável (risco extremo)", IF(R61&gt;200,"Significativo (risco muito alto)", IF(R61&gt;70,"Significativo (alto risco)", IF(R61&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="S61:S92" si="8">IF(R61&gt;400,"Insustentável (risco extremo)", IF(R61&gt;200,"Significativo (risco muito alto)", IF(R61&gt;70,"Significativo (alto risco)", IF(R61&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="T61" s="67" t="s">
@@ -27078,18 +27078,18 @@
         <v>0.2</v>
       </c>
       <c r="Z61" s="77">
-        <f>PRODUCT(W61:Y61)</f>
+        <f t="shared" ref="Z61:Z92" si="9">PRODUCT(W61:Y61)</f>
         <v>3.6</v>
       </c>
       <c r="AA61" s="75" t="str">
-        <f>IF(Z61&gt;400,"Insustentável (risco extremo)", IF(Z61&gt;200,"Significativo (risco muito alto)", IF(Z61&gt;70,"Significativo (alto risco)", IF(Z61&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="AA61:AA92" si="10">IF(Z61&gt;400,"Insustentável (risco extremo)", IF(Z61&gt;200,"Significativo (risco muito alto)", IF(Z61&gt;70,"Significativo (alto risco)", IF(Z61&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="AB61" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="62" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A62" s="50">
         <v>78</v>
       </c>
@@ -27142,11 +27142,11 @@
         <v>0.5</v>
       </c>
       <c r="R62" s="74">
-        <f>PRODUCT(O62:Q62)</f>
+        <f t="shared" si="7"/>
         <v>45</v>
       </c>
       <c r="S62" s="75" t="str">
-        <f>IF(R62&gt;400,"Insustentável (risco extremo)", IF(R62&gt;200,"Significativo (risco muito alto)", IF(R62&gt;70,"Significativo (alto risco)", IF(R62&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T62" s="67" t="s">
@@ -27168,18 +27168,18 @@
         <v>0.2</v>
       </c>
       <c r="Z62" s="77">
-        <f>PRODUCT(W62:Y62)</f>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="AA62" s="75" t="str">
-        <f>IF(Z62&gt;400,"Insustentável (risco extremo)", IF(Z62&gt;200,"Significativo (risco muito alto)", IF(Z62&gt;70,"Significativo (alto risco)", IF(Z62&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB62" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="63" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A63" s="50">
         <v>79</v>
       </c>
@@ -27232,11 +27232,11 @@
         <v>1</v>
       </c>
       <c r="R63" s="74">
-        <f>PRODUCT(O63:Q63)</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="S63" s="75" t="str">
-        <f>IF(R63&gt;400,"Insustentável (risco extremo)", IF(R63&gt;200,"Significativo (risco muito alto)", IF(R63&gt;70,"Significativo (alto risco)", IF(R63&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T63" s="67" t="s">
@@ -27258,18 +27258,18 @@
         <v>0.5</v>
       </c>
       <c r="Z63" s="77">
-        <f>PRODUCT(W63:Y63)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="AA63" s="75" t="str">
-        <f>IF(Z63&gt;400,"Insustentável (risco extremo)", IF(Z63&gt;200,"Significativo (risco muito alto)", IF(Z63&gt;70,"Significativo (alto risco)", IF(Z63&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB63" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="64" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A64" s="50"/>
       <c r="B64" s="78" t="s">
         <v>26</v>
@@ -27320,11 +27320,11 @@
         <v>0.5</v>
       </c>
       <c r="R64" s="74">
-        <f>PRODUCT(O64:Q64)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S64" s="75" t="str">
-        <f>IF(R64&gt;400,"Insustentável (risco extremo)", IF(R64&gt;200,"Significativo (risco muito alto)", IF(R64&gt;70,"Significativo (alto risco)", IF(R64&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T64" s="67" t="s">
@@ -27346,18 +27346,18 @@
         <v>0.1</v>
       </c>
       <c r="Z64" s="77">
-        <f>PRODUCT(W64:Y64)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA64" s="75" t="str">
-        <f>IF(Z64&gt;400,"Insustentável (risco extremo)", IF(Z64&gt;200,"Significativo (risco muito alto)", IF(Z64&gt;70,"Significativo (alto risco)", IF(Z64&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB64" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="65" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A65" s="50">
         <v>80</v>
       </c>
@@ -27410,11 +27410,11 @@
         <v>0.5</v>
       </c>
       <c r="R65" s="74">
-        <f>PRODUCT(O65:Q65)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S65" s="75" t="str">
-        <f>IF(R65&gt;400,"Insustentável (risco extremo)", IF(R65&gt;200,"Significativo (risco muito alto)", IF(R65&gt;70,"Significativo (alto risco)", IF(R65&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T65" s="67" t="s">
@@ -27436,18 +27436,18 @@
         <v>0.1</v>
       </c>
       <c r="Z65" s="77">
-        <f>PRODUCT(W65:Y65)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA65" s="75" t="str">
-        <f>IF(Z65&gt;400,"Insustentável (risco extremo)", IF(Z65&gt;200,"Significativo (risco muito alto)", IF(Z65&gt;70,"Significativo (alto risco)", IF(Z65&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB65" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="66" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="66" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A66" s="50">
         <v>81</v>
       </c>
@@ -27500,11 +27500,11 @@
         <v>0.5</v>
       </c>
       <c r="R66" s="74">
-        <f>PRODUCT(O66:Q66)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S66" s="75" t="str">
-        <f>IF(R66&gt;400,"Insustentável (risco extremo)", IF(R66&gt;200,"Significativo (risco muito alto)", IF(R66&gt;70,"Significativo (alto risco)", IF(R66&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T66" s="67" t="s">
@@ -27526,18 +27526,18 @@
         <v>0.1</v>
       </c>
       <c r="Z66" s="77">
-        <f>PRODUCT(W66:Y66)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA66" s="75" t="str">
-        <f>IF(Z66&gt;400,"Insustentável (risco extremo)", IF(Z66&gt;200,"Significativo (risco muito alto)", IF(Z66&gt;70,"Significativo (alto risco)", IF(Z66&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB66" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="67" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="67" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A67" s="50">
         <v>82</v>
       </c>
@@ -27590,11 +27590,11 @@
         <v>0.5</v>
       </c>
       <c r="R67" s="74">
-        <f>PRODUCT(O67:Q67)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="S67" s="75" t="str">
-        <f>IF(R67&gt;400,"Insustentável (risco extremo)", IF(R67&gt;200,"Significativo (risco muito alto)", IF(R67&gt;70,"Significativo (alto risco)", IF(R67&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T67" s="67" t="s">
@@ -27616,18 +27616,18 @@
         <v>0.1</v>
       </c>
       <c r="Z67" s="77">
-        <f>PRODUCT(W67:Y67)</f>
+        <f t="shared" si="9"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA67" s="75" t="str">
-        <f>IF(Z67&gt;400,"Insustentável (risco extremo)", IF(Z67&gt;200,"Significativo (risco muito alto)", IF(Z67&gt;70,"Significativo (alto risco)", IF(Z67&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB67" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="68" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A68" s="50">
         <v>85</v>
       </c>
@@ -27680,11 +27680,11 @@
         <v>0.1</v>
       </c>
       <c r="R68" s="74">
-        <f>PRODUCT(O68:Q68)</f>
+        <f t="shared" si="7"/>
         <v>1.8</v>
       </c>
       <c r="S68" s="75" t="str">
-        <f>IF(R68&gt;400,"Insustentável (risco extremo)", IF(R68&gt;200,"Significativo (risco muito alto)", IF(R68&gt;70,"Significativo (alto risco)", IF(R68&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T68" s="67" t="s">
@@ -27706,18 +27706,18 @@
         <v>0.1</v>
       </c>
       <c r="Z68" s="77">
-        <f>PRODUCT(W68:Y68)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA68" s="75" t="str">
-        <f>IF(Z68&gt;400,"Insustentável (risco extremo)", IF(Z68&gt;200,"Significativo (risco muito alto)", IF(Z68&gt;70,"Significativo (alto risco)", IF(Z68&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB68" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="69" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="69" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A69" s="50">
         <v>87</v>
       </c>
@@ -27770,11 +27770,11 @@
         <v>0.5</v>
       </c>
       <c r="R69" s="74">
-        <f>PRODUCT(O69:Q69)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="S69" s="75" t="str">
-        <f>IF(R69&gt;400,"Insustentável (risco extremo)", IF(R69&gt;200,"Significativo (risco muito alto)", IF(R69&gt;70,"Significativo (alto risco)", IF(R69&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T69" s="67" t="s">
@@ -27796,18 +27796,18 @@
         <v>0.2</v>
       </c>
       <c r="Z69" s="77">
-        <f>PRODUCT(W69:Y69)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA69" s="75" t="str">
-        <f>IF(Z69&gt;400,"Insustentável (risco extremo)", IF(Z69&gt;200,"Significativo (risco muito alto)", IF(Z69&gt;70,"Significativo (alto risco)", IF(Z69&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB69" s="67" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="70" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="70" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A70" s="50">
         <v>88</v>
       </c>
@@ -27860,11 +27860,11 @@
         <v>0.5</v>
       </c>
       <c r="R70" s="74">
-        <f>PRODUCT(O70:Q70)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="S70" s="75" t="str">
-        <f>IF(R70&gt;400,"Insustentável (risco extremo)", IF(R70&gt;200,"Significativo (risco muito alto)", IF(R70&gt;70,"Significativo (alto risco)", IF(R70&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T70" s="67" t="s">
@@ -27886,18 +27886,18 @@
         <v>0.2</v>
       </c>
       <c r="Z70" s="77">
-        <f>PRODUCT(W70:Y70)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA70" s="75" t="str">
-        <f>IF(Z70&gt;400,"Insustentável (risco extremo)", IF(Z70&gt;200,"Significativo (risco muito alto)", IF(Z70&gt;70,"Significativo (alto risco)", IF(Z70&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB70" s="67" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="71" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A71" s="50">
         <v>89</v>
       </c>
@@ -27950,11 +27950,11 @@
         <v>0.2</v>
       </c>
       <c r="R71" s="74">
-        <f>PRODUCT(O71:Q71)</f>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="S71" s="75" t="str">
-        <f>IF(R71&gt;400,"Insustentável (risco extremo)", IF(R71&gt;200,"Significativo (risco muito alto)", IF(R71&gt;70,"Significativo (alto risco)", IF(R71&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T71" s="67" t="s">
@@ -27976,18 +27976,18 @@
         <v>0.2</v>
       </c>
       <c r="Z71" s="77">
-        <f>PRODUCT(W71:Y71)</f>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AA71" s="75" t="str">
-        <f>IF(Z71&gt;400,"Insustentável (risco extremo)", IF(Z71&gt;200,"Significativo (risco muito alto)", IF(Z71&gt;70,"Significativo (alto risco)", IF(Z71&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB71" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="72" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="72" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A72" s="50">
         <v>90</v>
       </c>
@@ -28040,11 +28040,11 @@
         <v>0.5</v>
       </c>
       <c r="R72" s="74">
-        <f>PRODUCT(O72:Q72)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="S72" s="75" t="str">
-        <f>IF(R72&gt;400,"Insustentável (risco extremo)", IF(R72&gt;200,"Significativo (risco muito alto)", IF(R72&gt;70,"Significativo (alto risco)", IF(R72&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T72" s="67" t="s">
@@ -28066,18 +28066,18 @@
         <v>0.2</v>
       </c>
       <c r="Z72" s="77">
-        <f>PRODUCT(W72:Y72)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA72" s="75" t="str">
-        <f>IF(Z72&gt;400,"Insustentável (risco extremo)", IF(Z72&gt;200,"Significativo (risco muito alto)", IF(Z72&gt;70,"Significativo (alto risco)", IF(Z72&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB72" s="67" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="73" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="73" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A73" s="50">
         <v>91</v>
       </c>
@@ -28130,11 +28130,11 @@
         <v>0.5</v>
       </c>
       <c r="R73" s="74">
-        <f>PRODUCT(O73:Q73)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S73" s="75" t="str">
-        <f>IF(R73&gt;400,"Insustentável (risco extremo)", IF(R73&gt;200,"Significativo (risco muito alto)", IF(R73&gt;70,"Significativo (alto risco)", IF(R73&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T73" s="67" t="s">
@@ -28156,18 +28156,18 @@
         <v>0.1</v>
       </c>
       <c r="Z73" s="77">
-        <f>PRODUCT(W73:Y73)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA73" s="75" t="str">
-        <f>IF(Z73&gt;400,"Insustentável (risco extremo)", IF(Z73&gt;200,"Significativo (risco muito alto)", IF(Z73&gt;70,"Significativo (alto risco)", IF(Z73&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB73" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="74" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A74" s="50">
         <v>93</v>
       </c>
@@ -28220,11 +28220,11 @@
         <v>0.2</v>
       </c>
       <c r="R74" s="74">
-        <f>PRODUCT(O74:Q74)</f>
+        <f t="shared" si="7"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="S74" s="75" t="str">
-        <f>IF(R74&gt;400,"Insustentável (risco extremo)", IF(R74&gt;200,"Significativo (risco muito alto)", IF(R74&gt;70,"Significativo (alto risco)", IF(R74&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T74" s="67" t="s">
@@ -28246,18 +28246,18 @@
         <v>0.2</v>
       </c>
       <c r="Z74" s="77">
-        <f>PRODUCT(W74:Y74)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA74" s="75" t="str">
-        <f>IF(Z74&gt;400,"Insustentável (risco extremo)", IF(Z74&gt;200,"Significativo (risco muito alto)", IF(Z74&gt;70,"Significativo (alto risco)", IF(Z74&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB74" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="75" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="75" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A75" s="50">
         <v>94</v>
       </c>
@@ -28310,11 +28310,11 @@
         <v>0.2</v>
       </c>
       <c r="R75" s="74">
-        <f>PRODUCT(O75:Q75)</f>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="S75" s="75" t="str">
-        <f>IF(R75&gt;400,"Insustentável (risco extremo)", IF(R75&gt;200,"Significativo (risco muito alto)", IF(R75&gt;70,"Significativo (alto risco)", IF(R75&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T75" s="67" t="s">
@@ -28336,18 +28336,18 @@
         <v>0.2</v>
       </c>
       <c r="Z75" s="77">
-        <f>PRODUCT(W75:Y75)</f>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AA75" s="75" t="str">
-        <f>IF(Z75&gt;400,"Insustentável (risco extremo)", IF(Z75&gt;200,"Significativo (risco muito alto)", IF(Z75&gt;70,"Significativo (alto risco)", IF(Z75&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB75" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="76" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="76" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A76" s="50">
         <v>95</v>
       </c>
@@ -28400,11 +28400,11 @@
         <v>0.2</v>
       </c>
       <c r="R76" s="74">
-        <f>PRODUCT(O76:Q76)</f>
+        <f t="shared" si="7"/>
         <v>3.6</v>
       </c>
       <c r="S76" s="75" t="str">
-        <f>IF(R76&gt;400,"Insustentável (risco extremo)", IF(R76&gt;200,"Significativo (risco muito alto)", IF(R76&gt;70,"Significativo (alto risco)", IF(R76&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T76" s="67" t="s">
@@ -28426,18 +28426,18 @@
         <v>0.2</v>
       </c>
       <c r="Z76" s="77">
-        <f>PRODUCT(W76:Y76)</f>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AA76" s="75" t="str">
-        <f>IF(Z76&gt;400,"Insustentável (risco extremo)", IF(Z76&gt;200,"Significativo (risco muito alto)", IF(Z76&gt;70,"Significativo (alto risco)", IF(Z76&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB76" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="77" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="77" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A77" s="50">
         <v>97</v>
       </c>
@@ -28490,11 +28490,11 @@
         <v>0.5</v>
       </c>
       <c r="R77" s="74">
-        <f>PRODUCT(O77:Q77)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S77" s="75" t="str">
-        <f>IF(R77&gt;400,"Insustentável (risco extremo)", IF(R77&gt;200,"Significativo (risco muito alto)", IF(R77&gt;70,"Significativo (alto risco)", IF(R77&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T77" s="67" t="s">
@@ -28516,18 +28516,18 @@
         <v>0.1</v>
       </c>
       <c r="Z77" s="77">
-        <f>PRODUCT(W77:Y77)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA77" s="75" t="str">
-        <f>IF(Z77&gt;400,"Insustentável (risco extremo)", IF(Z77&gt;200,"Significativo (risco muito alto)", IF(Z77&gt;70,"Significativo (alto risco)", IF(Z77&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB77" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="78" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="78" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A78" s="50">
         <v>100</v>
       </c>
@@ -28580,11 +28580,11 @@
         <v>1</v>
       </c>
       <c r="R78" s="74">
-        <f>PRODUCT(O78:Q78)</f>
+        <f t="shared" si="7"/>
         <v>80</v>
       </c>
       <c r="S78" s="75" t="str">
-        <f>IF(R78&gt;400,"Insustentável (risco extremo)", IF(R78&gt;200,"Significativo (risco muito alto)", IF(R78&gt;70,"Significativo (alto risco)", IF(R78&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T78" s="67" t="s">
@@ -28606,18 +28606,18 @@
         <v>0.5</v>
       </c>
       <c r="Z78" s="77">
-        <f>PRODUCT(W78:Y78)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="AA78" s="75" t="str">
-        <f>IF(Z78&gt;400,"Insustentável (risco extremo)", IF(Z78&gt;200,"Significativo (risco muito alto)", IF(Z78&gt;70,"Significativo (alto risco)", IF(Z78&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB78" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="79" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="79" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A79" s="50">
         <v>101</v>
       </c>
@@ -28670,11 +28670,11 @@
         <v>1</v>
       </c>
       <c r="R79" s="74">
-        <f>PRODUCT(O79:Q79)</f>
+        <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="S79" s="75" t="str">
-        <f>IF(R79&gt;400,"Insustentável (risco extremo)", IF(R79&gt;200,"Significativo (risco muito alto)", IF(R79&gt;70,"Significativo (alto risco)", IF(R79&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T79" s="67" t="s">
@@ -28696,18 +28696,18 @@
         <v>0.5</v>
       </c>
       <c r="Z79" s="77">
-        <f>PRODUCT(W79:Y79)</f>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="AA79" s="75" t="str">
-        <f>IF(Z79&gt;400,"Insustentável (risco extremo)", IF(Z79&gt;200,"Significativo (risco muito alto)", IF(Z79&gt;70,"Significativo (alto risco)", IF(Z79&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB79" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="80" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="80" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A80" s="50">
         <v>102</v>
       </c>
@@ -28760,11 +28760,11 @@
         <v>0.2</v>
       </c>
       <c r="R80" s="74">
-        <f>PRODUCT(O80:Q80)</f>
+        <f t="shared" si="7"/>
         <v>48</v>
       </c>
       <c r="S80" s="75" t="str">
-        <f>IF(R80&gt;400,"Insustentável (risco extremo)", IF(R80&gt;200,"Significativo (risco muito alto)", IF(R80&gt;70,"Significativo (alto risco)", IF(R80&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T80" s="67" t="s">
@@ -28786,18 +28786,18 @@
         <v>0.2</v>
       </c>
       <c r="Z80" s="77">
-        <f>PRODUCT(W80:Y80)</f>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AA80" s="75" t="str">
-        <f>IF(Z80&gt;400,"Insustentável (risco extremo)", IF(Z80&gt;200,"Significativo (risco muito alto)", IF(Z80&gt;70,"Significativo (alto risco)", IF(Z80&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB80" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="81" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A81" s="50">
         <v>103</v>
       </c>
@@ -28850,11 +28850,11 @@
         <v>0.5</v>
       </c>
       <c r="R81" s="74">
-        <f>PRODUCT(O81:Q81)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S81" s="75" t="str">
-        <f>IF(R81&gt;400,"Insustentável (risco extremo)", IF(R81&gt;200,"Significativo (risco muito alto)", IF(R81&gt;70,"Significativo (alto risco)", IF(R81&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T81" s="67" t="s">
@@ -28876,18 +28876,18 @@
         <v>0.5</v>
       </c>
       <c r="Z81" s="77">
-        <f>PRODUCT(W81:Y81)</f>
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
       <c r="AA81" s="75" t="str">
-        <f>IF(Z81&gt;400,"Insustentável (risco extremo)", IF(Z81&gt;200,"Significativo (risco muito alto)", IF(Z81&gt;70,"Significativo (alto risco)", IF(Z81&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB81" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="82" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="82" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A82" s="50">
         <v>104</v>
       </c>
@@ -28940,11 +28940,11 @@
         <v>1</v>
       </c>
       <c r="R82" s="74">
-        <f>PRODUCT(O82:Q82)</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="S82" s="75" t="str">
-        <f>IF(R82&gt;400,"Insustentável (risco extremo)", IF(R82&gt;200,"Significativo (risco muito alto)", IF(R82&gt;70,"Significativo (alto risco)", IF(R82&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T82" s="67" t="s">
@@ -28966,18 +28966,18 @@
         <v>0.5</v>
       </c>
       <c r="Z82" s="77">
-        <f>PRODUCT(W82:Y82)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="AA82" s="75" t="str">
-        <f>IF(Z82&gt;400,"Insustentável (risco extremo)", IF(Z82&gt;200,"Significativo (risco muito alto)", IF(Z82&gt;70,"Significativo (alto risco)", IF(Z82&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB82" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="83" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="83" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A83" s="50">
         <v>105</v>
       </c>
@@ -29030,11 +29030,11 @@
         <v>0.5</v>
       </c>
       <c r="R83" s="74">
-        <f>PRODUCT(O83:Q83)</f>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="S83" s="75" t="str">
-        <f>IF(R83&gt;400,"Insustentável (risco extremo)", IF(R83&gt;200,"Significativo (risco muito alto)", IF(R83&gt;70,"Significativo (alto risco)", IF(R83&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T83" s="67" t="s">
@@ -29056,18 +29056,18 @@
         <v>0.5</v>
       </c>
       <c r="Z83" s="77">
-        <f>PRODUCT(W83:Y83)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="AA83" s="75" t="str">
-        <f>IF(Z83&gt;400,"Insustentável (risco extremo)", IF(Z83&gt;200,"Significativo (risco muito alto)", IF(Z83&gt;70,"Significativo (alto risco)", IF(Z83&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB83" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="84" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="84" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A84" s="50">
         <v>106</v>
       </c>
@@ -29120,11 +29120,11 @@
         <v>0.5</v>
       </c>
       <c r="R84" s="74">
-        <f>PRODUCT(O84:Q84)</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="S84" s="75" t="str">
-        <f>IF(R84&gt;400,"Insustentável (risco extremo)", IF(R84&gt;200,"Significativo (risco muito alto)", IF(R84&gt;70,"Significativo (alto risco)", IF(R84&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T84" s="67" t="s">
@@ -29146,18 +29146,18 @@
         <v>0.5</v>
       </c>
       <c r="Z84" s="77">
-        <f>PRODUCT(W84:Y84)</f>
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
       <c r="AA84" s="75" t="str">
-        <f>IF(Z84&gt;400,"Insustentável (risco extremo)", IF(Z84&gt;200,"Significativo (risco muito alto)", IF(Z84&gt;70,"Significativo (alto risco)", IF(Z84&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB84" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="85" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="85" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A85" s="50">
         <v>107</v>
       </c>
@@ -29210,11 +29210,11 @@
         <v>0.5</v>
       </c>
       <c r="R85" s="74">
-        <f>PRODUCT(O85:Q85)</f>
+        <f t="shared" si="7"/>
         <v>4.5</v>
       </c>
       <c r="S85" s="75" t="str">
-        <f>IF(R85&gt;400,"Insustentável (risco extremo)", IF(R85&gt;200,"Significativo (risco muito alto)", IF(R85&gt;70,"Significativo (alto risco)", IF(R85&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T85" s="67" t="s">
@@ -29236,18 +29236,18 @@
         <v>0.2</v>
       </c>
       <c r="Z85" s="77">
-        <f>PRODUCT(W85:Y85)</f>
+        <f t="shared" si="9"/>
         <v>1.8</v>
       </c>
       <c r="AA85" s="75" t="str">
-        <f>IF(Z85&gt;400,"Insustentável (risco extremo)", IF(Z85&gt;200,"Significativo (risco muito alto)", IF(Z85&gt;70,"Significativo (alto risco)", IF(Z85&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB85" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="86" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="86" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A86" s="50">
         <v>108</v>
       </c>
@@ -29263,7 +29263,7 @@
       <c r="E86" s="67" t="s">
         <v>375</v>
       </c>
-      <c r="F86" s="146" t="s">
+      <c r="F86" s="105" t="s">
         <v>54</v>
       </c>
       <c r="G86" s="67" t="s">
@@ -29300,11 +29300,11 @@
         <v>0.5</v>
       </c>
       <c r="R86" s="74">
-        <f>PRODUCT(O86:Q86)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="S86" s="75" t="str">
-        <f>IF(R86&gt;400,"Insustentável (risco extremo)", IF(R86&gt;200,"Significativo (risco muito alto)", IF(R86&gt;70,"Significativo (alto risco)", IF(R86&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T86" s="67" t="s">
@@ -29326,18 +29326,18 @@
         <v>0.2</v>
       </c>
       <c r="Z86" s="77">
-        <f>PRODUCT(W86:Y86)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="AA86" s="75" t="str">
-        <f>IF(Z86&gt;400,"Insustentável (risco extremo)", IF(Z86&gt;200,"Significativo (risco muito alto)", IF(Z86&gt;70,"Significativo (alto risco)", IF(Z86&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB86" s="80" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="87" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A87" s="50">
         <v>110</v>
       </c>
@@ -29390,11 +29390,11 @@
         <v>0.5</v>
       </c>
       <c r="R87" s="74">
-        <f>PRODUCT(O87:Q87)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S87" s="75" t="str">
-        <f>IF(R87&gt;400,"Insustentável (risco extremo)", IF(R87&gt;200,"Significativo (risco muito alto)", IF(R87&gt;70,"Significativo (alto risco)", IF(R87&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T87" s="67" t="s">
@@ -29416,18 +29416,18 @@
         <v>0.2</v>
       </c>
       <c r="Z87" s="77">
-        <f>PRODUCT(W87:Y87)</f>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AA87" s="75" t="str">
-        <f>IF(Z87&gt;400,"Insustentável (risco extremo)", IF(Z87&gt;200,"Significativo (risco muito alto)", IF(Z87&gt;70,"Significativo (alto risco)", IF(Z87&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB87" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="88" spans="1:28" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="88" spans="1:28" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A88" s="50">
         <v>111</v>
       </c>
@@ -29480,11 +29480,11 @@
         <v>0.5</v>
       </c>
       <c r="R88" s="74">
-        <f>PRODUCT(O88:Q88)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="S88" s="75" t="str">
-        <f>IF(R88&gt;400,"Insustentável (risco extremo)", IF(R88&gt;200,"Significativo (risco muito alto)", IF(R88&gt;70,"Significativo (alto risco)", IF(R88&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T88" s="67" t="s">
@@ -29506,18 +29506,18 @@
         <v>0.2</v>
       </c>
       <c r="Z88" s="77">
-        <f>PRODUCT(W88:Y88)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="AA88" s="75" t="str">
-        <f>IF(Z88&gt;400,"Insustentável (risco extremo)", IF(Z88&gt;200,"Significativo (risco muito alto)", IF(Z88&gt;70,"Significativo (alto risco)", IF(Z88&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB88" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="89" spans="1:28" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="89" spans="1:28" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A89" s="50">
         <v>113</v>
       </c>
@@ -29570,11 +29570,11 @@
         <v>0.5</v>
       </c>
       <c r="R89" s="74">
-        <f>PRODUCT(O89:Q89)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="S89" s="75" t="str">
-        <f>IF(R89&gt;400,"Insustentável (risco extremo)", IF(R89&gt;200,"Significativo (risco muito alto)", IF(R89&gt;70,"Significativo (alto risco)", IF(R89&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T89" s="67" t="s">
@@ -29596,18 +29596,18 @@
         <v>0.2</v>
       </c>
       <c r="Z89" s="77">
-        <f>PRODUCT(W89:Y89)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="AA89" s="75" t="str">
-        <f>IF(Z89&gt;400,"Insustentável (risco extremo)", IF(Z89&gt;200,"Significativo (risco muito alto)", IF(Z89&gt;70,"Significativo (alto risco)", IF(Z89&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB89" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="90" spans="1:28" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="90" spans="1:28" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A90" s="50">
         <v>114</v>
       </c>
@@ -29660,11 +29660,11 @@
         <v>0.5</v>
       </c>
       <c r="R90" s="74">
-        <f>PRODUCT(O90:Q90)</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="S90" s="75" t="str">
-        <f>IF(R90&gt;400,"Insustentável (risco extremo)", IF(R90&gt;200,"Significativo (risco muito alto)", IF(R90&gt;70,"Significativo (alto risco)", IF(R90&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T90" s="67" t="s">
@@ -29686,18 +29686,18 @@
         <v>0.2</v>
       </c>
       <c r="Z90" s="77">
-        <f>PRODUCT(W90:Y90)</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="AA90" s="75" t="str">
-        <f>IF(Z90&gt;400,"Insustentável (risco extremo)", IF(Z90&gt;200,"Significativo (risco muito alto)", IF(Z90&gt;70,"Significativo (alto risco)", IF(Z90&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB90" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="91" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="91" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A91" s="50">
         <v>115</v>
       </c>
@@ -29750,11 +29750,11 @@
         <v>0.5</v>
       </c>
       <c r="R91" s="74">
-        <f>PRODUCT(O91:Q91)</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="S91" s="75" t="str">
-        <f>IF(R91&gt;400,"Insustentável (risco extremo)", IF(R91&gt;200,"Significativo (risco muito alto)", IF(R91&gt;70,"Significativo (alto risco)", IF(R91&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T91" s="67" t="s">
@@ -29776,18 +29776,18 @@
         <v>0.2</v>
       </c>
       <c r="Z91" s="77">
-        <f>PRODUCT(W91:Y91)</f>
+        <f t="shared" si="9"/>
         <v>3.6</v>
       </c>
       <c r="AA91" s="75" t="str">
-        <f>IF(Z91&gt;400,"Insustentável (risco extremo)", IF(Z91&gt;200,"Significativo (risco muito alto)", IF(Z91&gt;70,"Significativo (alto risco)", IF(Z91&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB91" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="92" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="92" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A92" s="50">
         <v>116</v>
       </c>
@@ -29840,11 +29840,11 @@
         <v>0.2</v>
       </c>
       <c r="R92" s="74">
-        <f>PRODUCT(O92:Q92)</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="S92" s="75" t="str">
-        <f>IF(R92&gt;400,"Insustentável (risco extremo)", IF(R92&gt;200,"Significativo (risco muito alto)", IF(R92&gt;70,"Significativo (alto risco)", IF(R92&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="8"/>
         <v>Insignificante</v>
       </c>
       <c r="T92" s="67" t="s">
@@ -29866,18 +29866,18 @@
         <v>0.2</v>
       </c>
       <c r="Z92" s="77">
-        <f>PRODUCT(W92:Y92)</f>
+        <f t="shared" si="9"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA92" s="75" t="str">
-        <f>IF(Z92&gt;400,"Insustentável (risco extremo)", IF(Z92&gt;200,"Significativo (risco muito alto)", IF(Z92&gt;70,"Significativo (alto risco)", IF(Z92&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="10"/>
         <v>Insignificante</v>
       </c>
       <c r="AB92" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="93" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="93" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A93" s="50">
         <v>119</v>
       </c>
@@ -29930,11 +29930,11 @@
         <v>0.5</v>
       </c>
       <c r="R93" s="74">
-        <f>PRODUCT(O93:Q93)</f>
+        <f t="shared" ref="R93:R124" si="11">PRODUCT(O93:Q93)</f>
         <v>3</v>
       </c>
       <c r="S93" s="75" t="str">
-        <f>IF(R93&gt;400,"Insustentável (risco extremo)", IF(R93&gt;200,"Significativo (risco muito alto)", IF(R93&gt;70,"Significativo (alto risco)", IF(R93&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="S93:S124" si="12">IF(R93&gt;400,"Insustentável (risco extremo)", IF(R93&gt;200,"Significativo (risco muito alto)", IF(R93&gt;70,"Significativo (alto risco)", IF(R93&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="T93" s="67" t="s">
@@ -29956,18 +29956,18 @@
         <v>0.2</v>
       </c>
       <c r="Z93" s="77">
-        <f>PRODUCT(W93:Y93)</f>
+        <f t="shared" ref="Z93:Z124" si="13">PRODUCT(W93:Y93)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA93" s="75" t="str">
-        <f>IF(Z93&gt;400,"Insustentável (risco extremo)", IF(Z93&gt;200,"Significativo (risco muito alto)", IF(Z93&gt;70,"Significativo (alto risco)", IF(Z93&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="AA93:AA124" si="14">IF(Z93&gt;400,"Insustentável (risco extremo)", IF(Z93&gt;200,"Significativo (risco muito alto)", IF(Z93&gt;70,"Significativo (alto risco)", IF(Z93&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="AB93" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="94" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="94" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A94" s="50">
         <v>121</v>
       </c>
@@ -30020,11 +30020,11 @@
         <v>0.5</v>
       </c>
       <c r="R94" s="74">
-        <f>PRODUCT(O94:Q94)</f>
+        <f t="shared" si="11"/>
         <v>1.5</v>
       </c>
       <c r="S94" s="75" t="str">
-        <f>IF(R94&gt;400,"Insustentável (risco extremo)", IF(R94&gt;200,"Significativo (risco muito alto)", IF(R94&gt;70,"Significativo (alto risco)", IF(R94&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T94" s="67" t="s">
@@ -30046,18 +30046,18 @@
         <v>0.2</v>
       </c>
       <c r="Z94" s="77">
-        <f>PRODUCT(W94:Y94)</f>
+        <f t="shared" si="13"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA94" s="75" t="str">
-        <f>IF(Z94&gt;400,"Insustentável (risco extremo)", IF(Z94&gt;200,"Significativo (risco muito alto)", IF(Z94&gt;70,"Significativo (alto risco)", IF(Z94&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB94" s="67" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="95" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="95" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A95" s="50">
         <v>122</v>
       </c>
@@ -30110,11 +30110,11 @@
         <v>0.5</v>
       </c>
       <c r="R95" s="74">
-        <f>PRODUCT(O95:Q95)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="S95" s="75" t="str">
-        <f>IF(R95&gt;400,"Insustentável (risco extremo)", IF(R95&gt;200,"Significativo (risco muito alto)", IF(R95&gt;70,"Significativo (alto risco)", IF(R95&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T95" s="67" t="s">
@@ -30136,18 +30136,18 @@
         <v>0.5</v>
       </c>
       <c r="Z95" s="77">
-        <f>PRODUCT(W95:Y95)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="AA95" s="75" t="str">
-        <f>IF(Z95&gt;400,"Insustentável (risco extremo)", IF(Z95&gt;200,"Significativo (risco muito alto)", IF(Z95&gt;70,"Significativo (alto risco)", IF(Z95&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB95" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="96" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="96" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A96" s="50">
         <v>124</v>
       </c>
@@ -30200,11 +30200,11 @@
         <v>1</v>
       </c>
       <c r="R96" s="74">
-        <f>PRODUCT(O96:Q96)</f>
+        <f t="shared" si="11"/>
         <v>120</v>
       </c>
       <c r="S96" s="75" t="str">
-        <f>IF(R96&gt;400,"Insustentável (risco extremo)", IF(R96&gt;200,"Significativo (risco muito alto)", IF(R96&gt;70,"Significativo (alto risco)", IF(R96&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T96" s="67" t="s">
@@ -30226,18 +30226,18 @@
         <v>1</v>
       </c>
       <c r="Z96" s="77">
-        <f>PRODUCT(W96:Y96)</f>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="AA96" s="75" t="str">
-        <f>IF(Z96&gt;400,"Insustentável (risco extremo)", IF(Z96&gt;200,"Significativo (risco muito alto)", IF(Z96&gt;70,"Significativo (alto risco)", IF(Z96&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB96" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="97" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="97" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A97" s="50">
         <v>125</v>
       </c>
@@ -30290,11 +30290,11 @@
         <v>0.2</v>
       </c>
       <c r="R97" s="74">
-        <f>PRODUCT(O97:Q97)</f>
+        <f t="shared" si="11"/>
         <v>2.8000000000000003</v>
       </c>
       <c r="S97" s="75" t="str">
-        <f>IF(R97&gt;400,"Insustentável (risco extremo)", IF(R97&gt;200,"Significativo (risco muito alto)", IF(R97&gt;70,"Significativo (alto risco)", IF(R97&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T97" s="67" t="s">
@@ -30316,18 +30316,18 @@
         <v>0.2</v>
       </c>
       <c r="Z97" s="77">
-        <f>PRODUCT(W97:Y97)</f>
+        <f t="shared" si="13"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA97" s="75" t="str">
-        <f>IF(Z97&gt;400,"Insustentável (risco extremo)", IF(Z97&gt;200,"Significativo (risco muito alto)", IF(Z97&gt;70,"Significativo (alto risco)", IF(Z97&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB97" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="98" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="98" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A98" s="50">
         <v>126</v>
       </c>
@@ -30380,11 +30380,11 @@
         <v>0.5</v>
       </c>
       <c r="R98" s="74">
-        <f>PRODUCT(O98:Q98)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="S98" s="75" t="str">
-        <f>IF(R98&gt;400,"Insustentável (risco extremo)", IF(R98&gt;200,"Significativo (risco muito alto)", IF(R98&gt;70,"Significativo (alto risco)", IF(R98&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T98" s="67" t="s">
@@ -30406,18 +30406,18 @@
         <v>0.2</v>
       </c>
       <c r="Z98" s="77">
-        <f>PRODUCT(W98:Y98)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="AA98" s="75" t="str">
-        <f>IF(Z98&gt;400,"Insustentável (risco extremo)", IF(Z98&gt;200,"Significativo (risco muito alto)", IF(Z98&gt;70,"Significativo (alto risco)", IF(Z98&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB98" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="99" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="99" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A99" s="50">
         <v>127</v>
       </c>
@@ -30470,11 +30470,11 @@
         <v>1</v>
       </c>
       <c r="R99" s="74">
-        <f>PRODUCT(O99:Q99)</f>
+        <f t="shared" si="11"/>
         <v>14</v>
       </c>
       <c r="S99" s="75" t="str">
-        <f>IF(R99&gt;400,"Insustentável (risco extremo)", IF(R99&gt;200,"Significativo (risco muito alto)", IF(R99&gt;70,"Significativo (alto risco)", IF(R99&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T99" s="67" t="s">
@@ -30496,18 +30496,18 @@
         <v>0.5</v>
       </c>
       <c r="Z99" s="77">
-        <f>PRODUCT(W99:Y99)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="AA99" s="75" t="str">
-        <f>IF(Z99&gt;400,"Insustentável (risco extremo)", IF(Z99&gt;200,"Significativo (risco muito alto)", IF(Z99&gt;70,"Significativo (alto risco)", IF(Z99&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB99" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="100" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="100" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A100" s="50">
         <v>128</v>
       </c>
@@ -30560,11 +30560,11 @@
         <v>0.5</v>
       </c>
       <c r="R100" s="74">
-        <f>PRODUCT(O100:Q100)</f>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="S100" s="75" t="str">
-        <f>IF(R100&gt;400,"Insustentável (risco extremo)", IF(R100&gt;200,"Significativo (risco muito alto)", IF(R100&gt;70,"Significativo (alto risco)", IF(R100&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T100" s="67" t="s">
@@ -30586,18 +30586,18 @@
         <v>0.5</v>
       </c>
       <c r="Z100" s="77">
-        <f>PRODUCT(W100:Y100)</f>
+        <f t="shared" si="13"/>
         <v>3</v>
       </c>
       <c r="AA100" s="75" t="str">
-        <f>IF(Z100&gt;400,"Insustentável (risco extremo)", IF(Z100&gt;200,"Significativo (risco muito alto)", IF(Z100&gt;70,"Significativo (alto risco)", IF(Z100&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB100" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="101" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="101" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A101" s="50">
         <v>131</v>
       </c>
@@ -30650,11 +30650,11 @@
         <v>0.5</v>
       </c>
       <c r="R101" s="74">
-        <f>PRODUCT(O101:Q101)</f>
+        <f t="shared" si="11"/>
         <v>0.5</v>
       </c>
       <c r="S101" s="75" t="str">
-        <f>IF(R101&gt;400,"Insustentável (risco extremo)", IF(R101&gt;200,"Significativo (risco muito alto)", IF(R101&gt;70,"Significativo (alto risco)", IF(R101&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T101" s="67" t="s">
@@ -30676,18 +30676,18 @@
         <v>0.2</v>
       </c>
       <c r="Z101" s="77">
-        <f>PRODUCT(W101:Y101)</f>
+        <f t="shared" si="13"/>
         <v>0.2</v>
       </c>
       <c r="AA101" s="75" t="str">
-        <f>IF(Z101&gt;400,"Insustentável (risco extremo)", IF(Z101&gt;200,"Significativo (risco muito alto)", IF(Z101&gt;70,"Significativo (alto risco)", IF(Z101&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB101" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="102" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="102" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A102" s="50">
         <v>132</v>
       </c>
@@ -30740,11 +30740,11 @@
         <v>0.2</v>
       </c>
       <c r="R102" s="74">
-        <f>PRODUCT(O102:Q102)</f>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="S102" s="75" t="str">
-        <f>IF(R102&gt;400,"Insustentável (risco extremo)", IF(R102&gt;200,"Significativo (risco muito alto)", IF(R102&gt;70,"Significativo (alto risco)", IF(R102&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T102" s="67" t="s">
@@ -30766,18 +30766,18 @@
         <v>0.2</v>
       </c>
       <c r="Z102" s="77">
-        <f>PRODUCT(W102:Y102)</f>
+        <f t="shared" si="13"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA102" s="75" t="str">
-        <f>IF(Z102&gt;400,"Insustentável (risco extremo)", IF(Z102&gt;200,"Significativo (risco muito alto)", IF(Z102&gt;70,"Significativo (alto risco)", IF(Z102&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB102" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="103" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="103" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A103" s="50">
         <v>135</v>
       </c>
@@ -30830,11 +30830,11 @@
         <v>0.5</v>
       </c>
       <c r="R103" s="74">
-        <f>PRODUCT(O103:Q103)</f>
+        <f t="shared" si="11"/>
         <v>1.5</v>
       </c>
       <c r="S103" s="75" t="str">
-        <f>IF(R103&gt;400,"Insustentável (risco extremo)", IF(R103&gt;200,"Significativo (risco muito alto)", IF(R103&gt;70,"Significativo (alto risco)", IF(R103&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T103" s="67" t="s">
@@ -30856,18 +30856,18 @@
         <v>0.2</v>
       </c>
       <c r="Z103" s="77">
-        <f>PRODUCT(W103:Y103)</f>
+        <f t="shared" si="13"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA103" s="75" t="str">
-        <f>IF(Z103&gt;400,"Insustentável (risco extremo)", IF(Z103&gt;200,"Significativo (risco muito alto)", IF(Z103&gt;70,"Significativo (alto risco)", IF(Z103&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB103" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="104" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="104" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A104" s="50">
         <v>136</v>
       </c>
@@ -30920,11 +30920,11 @@
         <v>0.5</v>
       </c>
       <c r="R104" s="74">
-        <f>PRODUCT(O104:Q104)</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="S104" s="75" t="str">
-        <f>IF(R104&gt;400,"Insustentável (risco extremo)", IF(R104&gt;200,"Significativo (risco muito alto)", IF(R104&gt;70,"Significativo (alto risco)", IF(R104&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T104" s="67" t="s">
@@ -30946,18 +30946,18 @@
         <v>0.2</v>
       </c>
       <c r="Z104" s="77">
-        <f>PRODUCT(W104:Y104)</f>
+        <f t="shared" si="13"/>
         <v>3.6</v>
       </c>
       <c r="AA104" s="75" t="str">
-        <f>IF(Z104&gt;400,"Insustentável (risco extremo)", IF(Z104&gt;200,"Significativo (risco muito alto)", IF(Z104&gt;70,"Significativo (alto risco)", IF(Z104&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB104" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="105" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="105" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A105" s="50">
         <v>137</v>
       </c>
@@ -31010,11 +31010,11 @@
         <v>3</v>
       </c>
       <c r="R105" s="74">
-        <f>PRODUCT(O105:Q105)</f>
+        <f t="shared" si="11"/>
         <v>126</v>
       </c>
       <c r="S105" s="75" t="str">
-        <f>IF(R105&gt;400,"Insustentável (risco extremo)", IF(R105&gt;200,"Significativo (risco muito alto)", IF(R105&gt;70,"Significativo (alto risco)", IF(R105&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T105" s="80" t="s">
@@ -31036,18 +31036,18 @@
         <v>1</v>
       </c>
       <c r="Z105" s="77">
-        <f>PRODUCT(W105:Y105)</f>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="AA105" s="75" t="str">
-        <f>IF(Z105&gt;400,"Insustentável (risco extremo)", IF(Z105&gt;200,"Significativo (risco muito alto)", IF(Z105&gt;70,"Significativo (alto risco)", IF(Z105&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB105" s="80" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="106" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="106" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A106" s="50">
         <v>140</v>
       </c>
@@ -31100,11 +31100,11 @@
         <v>0.2</v>
       </c>
       <c r="R106" s="74">
-        <f>PRODUCT(O106:Q106)</f>
+        <f t="shared" si="11"/>
         <v>8</v>
       </c>
       <c r="S106" s="75" t="str">
-        <f>IF(R106&gt;400,"Insustentável (risco extremo)", IF(R106&gt;200,"Significativo (risco muito alto)", IF(R106&gt;70,"Significativo (alto risco)", IF(R106&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T106" s="80" t="s">
@@ -31126,18 +31126,18 @@
         <v>0.2</v>
       </c>
       <c r="Z106" s="77">
-        <f>PRODUCT(W106:Y106)</f>
+        <f t="shared" si="13"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA106" s="75" t="str">
-        <f>IF(Z106&gt;400,"Insustentável (risco extremo)", IF(Z106&gt;200,"Significativo (risco muito alto)", IF(Z106&gt;70,"Significativo (alto risco)", IF(Z106&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB106" s="80" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="107" spans="1:28" s="54" customFormat="1" ht="408" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="107" spans="1:28" s="54" customFormat="1" ht="408" hidden="1" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A107" s="50">
         <v>141</v>
       </c>
@@ -31190,11 +31190,11 @@
         <v>0.5</v>
       </c>
       <c r="R107" s="74">
-        <f>PRODUCT(O107:Q107)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="S107" s="75" t="str">
-        <f>IF(R107&gt;400,"Insustentável (risco extremo)", IF(R107&gt;200,"Significativo (risco muito alto)", IF(R107&gt;70,"Significativo (alto risco)", IF(R107&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T107" s="80" t="s">
@@ -31203,7 +31203,7 @@
       <c r="U107" s="80" t="s">
         <v>278</v>
       </c>
-      <c r="V107" s="149" t="s">
+      <c r="V107" s="108" t="s">
         <v>273</v>
       </c>
       <c r="W107" s="83">
@@ -31216,18 +31216,18 @@
         <v>0.2</v>
       </c>
       <c r="Z107" s="77">
-        <f>PRODUCT(W107:Y107)</f>
+        <f t="shared" si="13"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA107" s="75" t="str">
-        <f>IF(Z107&gt;400,"Insustentável (risco extremo)", IF(Z107&gt;200,"Significativo (risco muito alto)", IF(Z107&gt;70,"Significativo (alto risco)", IF(Z107&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB107" s="80" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="108" spans="1:28" s="54" customFormat="1" ht="408" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="108" spans="1:28" s="54" customFormat="1" ht="408" hidden="1" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A108" s="50">
         <v>142</v>
       </c>
@@ -31280,11 +31280,11 @@
         <v>0.2</v>
       </c>
       <c r="R108" s="74">
-        <f>PRODUCT(O108:Q108)</f>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="S108" s="75" t="str">
-        <f>IF(R108&gt;400,"Insustentável (risco extremo)", IF(R108&gt;200,"Significativo (risco muito alto)", IF(R108&gt;70,"Significativo (alto risco)", IF(R108&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T108" s="80" t="s">
@@ -31306,18 +31306,18 @@
         <v>0.2</v>
       </c>
       <c r="Z108" s="77">
-        <f>PRODUCT(W108:Y108)</f>
+        <f t="shared" si="13"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA108" s="75" t="str">
-        <f>IF(Z108&gt;400,"Insustentável (risco extremo)", IF(Z108&gt;200,"Significativo (risco muito alto)", IF(Z108&gt;70,"Significativo (alto risco)", IF(Z108&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB108" s="80" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="109" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="109" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A109" s="50">
         <v>146</v>
       </c>
@@ -31370,11 +31370,11 @@
         <v>0.5</v>
       </c>
       <c r="R109" s="74">
-        <f>PRODUCT(O109:Q109)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="S109" s="75" t="str">
-        <f>IF(R109&gt;400,"Insustentável (risco extremo)", IF(R109&gt;200,"Significativo (risco muito alto)", IF(R109&gt;70,"Significativo (alto risco)", IF(R109&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T109" s="67" t="s">
@@ -31396,18 +31396,18 @@
         <v>0.1</v>
       </c>
       <c r="Z109" s="77">
-        <f>PRODUCT(W109:Y109)</f>
+        <f t="shared" si="13"/>
         <v>1.8</v>
       </c>
       <c r="AA109" s="75" t="str">
-        <f>IF(Z109&gt;400,"Insustentável (risco extremo)", IF(Z109&gt;200,"Significativo (risco muito alto)", IF(Z109&gt;70,"Significativo (alto risco)", IF(Z109&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB109" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="110" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="110" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A110" s="50">
         <v>147</v>
       </c>
@@ -31460,11 +31460,11 @@
         <v>0.5</v>
       </c>
       <c r="R110" s="74">
-        <f>PRODUCT(O110:Q110)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="S110" s="75" t="str">
-        <f>IF(R110&gt;400,"Insustentável (risco extremo)", IF(R110&gt;200,"Significativo (risco muito alto)", IF(R110&gt;70,"Significativo (alto risco)", IF(R110&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T110" s="67" t="s">
@@ -31486,18 +31486,18 @@
         <v>0.2</v>
       </c>
       <c r="Z110" s="77">
-        <f>PRODUCT(W110:Y110)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="AA110" s="75" t="str">
-        <f>IF(Z110&gt;400,"Insustentável (risco extremo)", IF(Z110&gt;200,"Significativo (risco muito alto)", IF(Z110&gt;70,"Significativo (alto risco)", IF(Z110&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB110" s="67" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="111" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A111" s="50">
         <v>148</v>
       </c>
@@ -31550,20 +31550,20 @@
         <v>0.5</v>
       </c>
       <c r="R111" s="74">
-        <f>PRODUCT(O111:Q111)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="S111" s="75" t="str">
-        <f>IF(R111&gt;400,"Insustentável (risco extremo)", IF(R111&gt;200,"Significativo (risco muito alto)", IF(R111&gt;70,"Significativo (alto risco)", IF(R111&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T111" s="67" t="s">
         <v>271</v>
       </c>
-      <c r="U111" s="147" t="s">
+      <c r="U111" s="106" t="s">
         <v>272</v>
       </c>
-      <c r="V111" s="148" t="s">
+      <c r="V111" s="107" t="s">
         <v>273</v>
       </c>
       <c r="W111" s="76">
@@ -31576,18 +31576,18 @@
         <v>0.2</v>
       </c>
       <c r="Z111" s="77">
-        <f>PRODUCT(W111:Y111)</f>
+        <f t="shared" si="13"/>
         <v>6</v>
       </c>
       <c r="AA111" s="75" t="str">
-        <f>IF(Z111&gt;400,"Insustentável (risco extremo)", IF(Z111&gt;200,"Significativo (risco muito alto)", IF(Z111&gt;70,"Significativo (alto risco)", IF(Z111&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB111" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="112" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="112" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A112" s="50"/>
       <c r="B112" s="78" t="s">
         <v>26</v>
@@ -31638,11 +31638,11 @@
         <v>0.5</v>
       </c>
       <c r="R112" s="74">
-        <f>PRODUCT(O112:Q112)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="S112" s="75" t="str">
-        <f>IF(R112&gt;400,"Insustentável (risco extremo)", IF(R112&gt;200,"Significativo (risco muito alto)", IF(R112&gt;70,"Significativo (alto risco)", IF(R112&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T112" s="67" t="s">
@@ -31664,18 +31664,18 @@
         <v>0.2</v>
       </c>
       <c r="Z112" s="77">
-        <f>PRODUCT(W112:Y112)</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="AA112" s="75" t="str">
-        <f>IF(Z112&gt;400,"Insustentável (risco extremo)", IF(Z112&gt;200,"Significativo (risco muito alto)", IF(Z112&gt;70,"Significativo (alto risco)", IF(Z112&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB112" s="67" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="113" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="113" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A113" s="50">
         <v>149</v>
       </c>
@@ -31728,11 +31728,11 @@
         <v>1</v>
       </c>
       <c r="R113" s="74">
-        <f>PRODUCT(O113:Q113)</f>
+        <f t="shared" si="11"/>
         <v>30</v>
       </c>
       <c r="S113" s="75" t="str">
-        <f>IF(R113&gt;400,"Insustentável (risco extremo)", IF(R113&gt;200,"Significativo (risco muito alto)", IF(R113&gt;70,"Significativo (alto risco)", IF(R113&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T113" s="67" t="s">
@@ -31754,18 +31754,18 @@
         <v>0.1</v>
       </c>
       <c r="Z113" s="77">
-        <f>PRODUCT(W113:Y113)</f>
+        <f t="shared" si="13"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA113" s="75" t="str">
-        <f>IF(Z113&gt;400,"Insustentável (risco extremo)", IF(Z113&gt;200,"Significativo (risco muito alto)", IF(Z113&gt;70,"Significativo (alto risco)", IF(Z113&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB113" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="114" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A114" s="50">
         <v>151</v>
       </c>
@@ -31818,11 +31818,11 @@
         <v>0.5</v>
       </c>
       <c r="R114" s="74">
-        <f>PRODUCT(O114:Q114)</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="S114" s="75" t="str">
-        <f>IF(R114&gt;400,"Insustentável (risco extremo)", IF(R114&gt;200,"Significativo (risco muito alto)", IF(R114&gt;70,"Significativo (alto risco)", IF(R114&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T114" s="67" t="s">
@@ -31844,18 +31844,18 @@
         <v>0.2</v>
       </c>
       <c r="Z114" s="77">
-        <f>PRODUCT(W114:Y114)</f>
+        <f t="shared" si="13"/>
         <v>1.8</v>
       </c>
       <c r="AA114" s="75" t="str">
-        <f>IF(Z114&gt;400,"Insustentável (risco extremo)", IF(Z114&gt;200,"Significativo (risco muito alto)", IF(Z114&gt;70,"Significativo (alto risco)", IF(Z114&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB114" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="115" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="115" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A115" s="50">
         <v>155</v>
       </c>
@@ -31908,11 +31908,11 @@
         <v>1</v>
       </c>
       <c r="R115" s="74">
-        <f>PRODUCT(O115:Q115)</f>
+        <f t="shared" si="11"/>
         <v>150</v>
       </c>
       <c r="S115" s="75" t="str">
-        <f>IF(R115&gt;400,"Insustentável (risco extremo)", IF(R115&gt;200,"Significativo (risco muito alto)", IF(R115&gt;70,"Significativo (alto risco)", IF(R115&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T115" s="80" t="s">
@@ -31934,18 +31934,18 @@
         <v>1</v>
       </c>
       <c r="Z115" s="77">
-        <f>PRODUCT(W115:Y115)</f>
+        <f t="shared" si="13"/>
         <v>18</v>
       </c>
       <c r="AA115" s="75" t="str">
-        <f>IF(Z115&gt;400,"Insustentável (risco extremo)", IF(Z115&gt;200,"Significativo (risco muito alto)", IF(Z115&gt;70,"Significativo (alto risco)", IF(Z115&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB115" s="80" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="116" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="116" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A116" s="50">
         <v>156</v>
       </c>
@@ -31998,11 +31998,11 @@
         <v>1</v>
       </c>
       <c r="R116" s="74">
-        <f>PRODUCT(O116:Q116)</f>
+        <f t="shared" si="11"/>
         <v>18</v>
       </c>
       <c r="S116" s="75" t="str">
-        <f>IF(R116&gt;400,"Insustentável (risco extremo)", IF(R116&gt;200,"Significativo (risco muito alto)", IF(R116&gt;70,"Significativo (alto risco)", IF(R116&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T116" s="67" t="s">
@@ -32024,18 +32024,18 @@
         <v>0.1</v>
       </c>
       <c r="Z116" s="77">
-        <f>PRODUCT(W116:Y116)</f>
+        <f t="shared" si="13"/>
         <v>1.8</v>
       </c>
       <c r="AA116" s="75" t="str">
-        <f>IF(Z116&gt;400,"Insustentável (risco extremo)", IF(Z116&gt;200,"Significativo (risco muito alto)", IF(Z116&gt;70,"Significativo (alto risco)", IF(Z116&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB116" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="117" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="117" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A117" s="50">
         <v>157</v>
       </c>
@@ -32088,11 +32088,11 @@
         <v>1</v>
       </c>
       <c r="R117" s="74">
-        <f>PRODUCT(O117:Q117)</f>
+        <f t="shared" si="11"/>
         <v>30</v>
       </c>
       <c r="S117" s="75" t="str">
-        <f>IF(R117&gt;400,"Insustentável (risco extremo)", IF(R117&gt;200,"Significativo (risco muito alto)", IF(R117&gt;70,"Significativo (alto risco)", IF(R117&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T117" s="67" t="s">
@@ -32114,18 +32114,18 @@
         <v>0.5</v>
       </c>
       <c r="Z117" s="77">
-        <f>PRODUCT(W117:Y117)</f>
+        <f t="shared" si="13"/>
         <v>9</v>
       </c>
       <c r="AA117" s="75" t="str">
-        <f>IF(Z117&gt;400,"Insustentável (risco extremo)", IF(Z117&gt;200,"Significativo (risco muito alto)", IF(Z117&gt;70,"Significativo (alto risco)", IF(Z117&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB117" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="118" spans="1:28" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="118" spans="1:28" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A118" s="50">
         <v>160</v>
       </c>
@@ -32178,11 +32178,11 @@
         <v>0.5</v>
       </c>
       <c r="R118" s="74">
-        <f>PRODUCT(O118:Q118)</f>
+        <f t="shared" si="11"/>
         <v>3</v>
       </c>
       <c r="S118" s="75" t="str">
-        <f>IF(R118&gt;400,"Insustentável (risco extremo)", IF(R118&gt;200,"Significativo (risco muito alto)", IF(R118&gt;70,"Significativo (alto risco)", IF(R118&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T118" s="67" t="s">
@@ -32204,18 +32204,18 @@
         <v>0.2</v>
       </c>
       <c r="Z118" s="77">
-        <f>PRODUCT(W118:Y118)</f>
+        <f t="shared" si="13"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA118" s="75" t="str">
-        <f>IF(Z118&gt;400,"Insustentável (risco extremo)", IF(Z118&gt;200,"Significativo (risco muito alto)", IF(Z118&gt;70,"Significativo (alto risco)", IF(Z118&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB118" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="119" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="119" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A119" s="50">
         <v>161</v>
       </c>
@@ -32268,11 +32268,11 @@
         <v>0.5</v>
       </c>
       <c r="R119" s="74">
-        <f>PRODUCT(O119:Q119)</f>
+        <f t="shared" si="11"/>
         <v>9</v>
       </c>
       <c r="S119" s="75" t="str">
-        <f>IF(R119&gt;400,"Insustentável (risco extremo)", IF(R119&gt;200,"Significativo (risco muito alto)", IF(R119&gt;70,"Significativo (alto risco)", IF(R119&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T119" s="67" t="s">
@@ -32294,18 +32294,18 @@
         <v>0.2</v>
       </c>
       <c r="Z119" s="77">
-        <f>PRODUCT(W119:Y119)</f>
+        <f t="shared" si="13"/>
         <v>3.6</v>
       </c>
       <c r="AA119" s="75" t="str">
-        <f>IF(Z119&gt;400,"Insustentável (risco extremo)", IF(Z119&gt;200,"Significativo (risco muito alto)", IF(Z119&gt;70,"Significativo (alto risco)", IF(Z119&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB119" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="120" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="120" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A120" s="50">
         <v>162</v>
       </c>
@@ -32358,11 +32358,11 @@
         <v>0.5</v>
       </c>
       <c r="R120" s="74">
-        <f>PRODUCT(O120:Q120)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="S120" s="75" t="str">
-        <f>IF(R120&gt;400,"Insustentável (risco extremo)", IF(R120&gt;200,"Significativo (risco muito alto)", IF(R120&gt;70,"Significativo (alto risco)", IF(R120&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T120" s="80" t="s">
@@ -32387,14 +32387,14 @@
         <v>0.6</v>
       </c>
       <c r="AA120" s="75" t="str">
-        <f>IF(Z120&gt;400,"Insustentável (risco extremo)", IF(Z120&gt;200,"Significativo (risco muito alto)", IF(Z120&gt;70,"Significativo (alto risco)", IF(Z120&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB120" s="80" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="121" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="121" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A121" s="50">
         <v>164</v>
       </c>
@@ -32447,11 +32447,11 @@
         <v>0.5</v>
       </c>
       <c r="R121" s="74">
-        <f>PRODUCT(O121:Q121)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="S121" s="75" t="str">
-        <f>IF(R121&gt;400,"Insustentável (risco extremo)", IF(R121&gt;200,"Significativo (risco muito alto)", IF(R121&gt;70,"Significativo (alto risco)", IF(R121&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T121" s="67" t="s">
@@ -32473,18 +32473,18 @@
         <v>0.2</v>
       </c>
       <c r="Z121" s="77">
-        <f>PRODUCT(W121:Y121)</f>
+        <f t="shared" ref="Z121:Z156" si="15">PRODUCT(W121:Y121)</f>
         <v>6</v>
       </c>
       <c r="AA121" s="75" t="str">
-        <f>IF(Z121&gt;400,"Insustentável (risco extremo)", IF(Z121&gt;200,"Significativo (risco muito alto)", IF(Z121&gt;70,"Significativo (alto risco)", IF(Z121&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB121" s="67" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="122" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="122" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A122" s="50">
         <v>165</v>
       </c>
@@ -32537,11 +32537,11 @@
         <v>0.5</v>
       </c>
       <c r="R122" s="74">
-        <f>PRODUCT(O122:Q122)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="S122" s="75" t="str">
-        <f>IF(R122&gt;400,"Insustentável (risco extremo)", IF(R122&gt;200,"Significativo (risco muito alto)", IF(R122&gt;70,"Significativo (alto risco)", IF(R122&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T122" s="67" t="s">
@@ -32563,18 +32563,18 @@
         <v>0.2</v>
       </c>
       <c r="Z122" s="77">
-        <f>PRODUCT(W122:Y122)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="AA122" s="75" t="str">
-        <f>IF(Z122&gt;400,"Insustentável (risco extremo)", IF(Z122&gt;200,"Significativo (risco muito alto)", IF(Z122&gt;70,"Significativo (alto risco)", IF(Z122&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB122" s="67" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="123" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A123" s="50">
         <v>166</v>
       </c>
@@ -32627,11 +32627,11 @@
         <v>0.5</v>
       </c>
       <c r="R123" s="74">
-        <f>PRODUCT(O123:Q123)</f>
+        <f t="shared" si="11"/>
         <v>5</v>
       </c>
       <c r="S123" s="75" t="str">
-        <f>IF(R123&gt;400,"Insustentável (risco extremo)", IF(R123&gt;200,"Significativo (risco muito alto)", IF(R123&gt;70,"Significativo (alto risco)", IF(R123&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T123" s="67" t="s">
@@ -32653,18 +32653,18 @@
         <v>0.2</v>
       </c>
       <c r="Z123" s="77">
-        <f>PRODUCT(W123:Y123)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="AA123" s="75" t="str">
-        <f>IF(Z123&gt;400,"Insustentável (risco extremo)", IF(Z123&gt;200,"Significativo (risco muito alto)", IF(Z123&gt;70,"Significativo (alto risco)", IF(Z123&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB123" s="67" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="124" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A124" s="50">
         <v>168</v>
       </c>
@@ -32717,11 +32717,11 @@
         <v>0.5</v>
       </c>
       <c r="R124" s="74">
-        <f>PRODUCT(O124:Q124)</f>
+        <f t="shared" si="11"/>
         <v>15</v>
       </c>
       <c r="S124" s="75" t="str">
-        <f>IF(R124&gt;400,"Insustentável (risco extremo)", IF(R124&gt;200,"Significativo (risco muito alto)", IF(R124&gt;70,"Significativo (alto risco)", IF(R124&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="12"/>
         <v>Insignificante</v>
       </c>
       <c r="T124" s="67" t="s">
@@ -32743,18 +32743,18 @@
         <v>0.1</v>
       </c>
       <c r="Z124" s="77">
-        <f>PRODUCT(W124:Y124)</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AA124" s="75" t="str">
-        <f>IF(Z124&gt;400,"Insustentável (risco extremo)", IF(Z124&gt;200,"Significativo (risco muito alto)", IF(Z124&gt;70,"Significativo (alto risco)", IF(Z124&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="14"/>
         <v>Insignificante</v>
       </c>
       <c r="AB124" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="125" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="125" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A125" s="50">
         <v>169</v>
       </c>
@@ -32807,11 +32807,11 @@
         <v>0.5</v>
       </c>
       <c r="R125" s="74">
-        <f>PRODUCT(O125:Q125)</f>
+        <f t="shared" ref="R125:R156" si="16">PRODUCT(O125:Q125)</f>
         <v>15</v>
       </c>
       <c r="S125" s="75" t="str">
-        <f>IF(R125&gt;400,"Insustentável (risco extremo)", IF(R125&gt;200,"Significativo (risco muito alto)", IF(R125&gt;70,"Significativo (alto risco)", IF(R125&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="S125:S156" si="17">IF(R125&gt;400,"Insustentável (risco extremo)", IF(R125&gt;200,"Significativo (risco muito alto)", IF(R125&gt;70,"Significativo (alto risco)", IF(R125&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="T125" s="67" t="s">
@@ -32833,18 +32833,18 @@
         <v>0.2</v>
       </c>
       <c r="Z125" s="77">
-        <f>PRODUCT(W125:Y125)</f>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="AA125" s="75" t="str">
-        <f>IF(Z125&gt;400,"Insustentável (risco extremo)", IF(Z125&gt;200,"Significativo (risco muito alto)", IF(Z125&gt;70,"Significativo (alto risco)", IF(Z125&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="AA125:AA156" si="18">IF(Z125&gt;400,"Insustentável (risco extremo)", IF(Z125&gt;200,"Significativo (risco muito alto)", IF(Z125&gt;70,"Significativo (alto risco)", IF(Z125&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Insignificante</v>
       </c>
       <c r="AB125" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="126" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="126" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A126" s="50">
         <v>170</v>
       </c>
@@ -32897,11 +32897,11 @@
         <v>0.5</v>
       </c>
       <c r="R126" s="74">
-        <f>PRODUCT(O126:Q126)</f>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="S126" s="75" t="str">
-        <f>IF(R126&gt;400,"Insustentável (risco extremo)", IF(R126&gt;200,"Significativo (risco muito alto)", IF(R126&gt;70,"Significativo (alto risco)", IF(R126&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T126" s="67" t="s">
@@ -32923,18 +32923,18 @@
         <v>0.2</v>
       </c>
       <c r="Z126" s="77">
-        <f>PRODUCT(W126:Y126)</f>
+        <f t="shared" si="15"/>
         <v>3.6</v>
       </c>
       <c r="AA126" s="75" t="str">
-        <f>IF(Z126&gt;400,"Insustentável (risco extremo)", IF(Z126&gt;200,"Significativo (risco muito alto)", IF(Z126&gt;70,"Significativo (alto risco)", IF(Z126&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB126" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="127" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="127" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A127" s="50">
         <v>173</v>
       </c>
@@ -32987,11 +32987,11 @@
         <v>0.5</v>
       </c>
       <c r="R127" s="74">
-        <f>PRODUCT(O127:Q127)</f>
+        <f t="shared" si="16"/>
         <v>4.5</v>
       </c>
       <c r="S127" s="75" t="str">
-        <f>IF(R127&gt;400,"Insustentável (risco extremo)", IF(R127&gt;200,"Significativo (risco muito alto)", IF(R127&gt;70,"Significativo (alto risco)", IF(R127&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T127" s="67" t="s">
@@ -33013,18 +33013,18 @@
         <v>0.2</v>
       </c>
       <c r="Z127" s="77">
-        <f>PRODUCT(W127:Y127)</f>
+        <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA127" s="75" t="str">
-        <f>IF(Z127&gt;400,"Insustentável (risco extremo)", IF(Z127&gt;200,"Significativo (risco muito alto)", IF(Z127&gt;70,"Significativo (alto risco)", IF(Z127&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB127" s="80" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="128" spans="1:28" s="58" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="128" spans="1:28" s="58" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A128" s="50">
         <v>175</v>
       </c>
@@ -33077,11 +33077,11 @@
         <v>0.5</v>
       </c>
       <c r="R128" s="74">
-        <f>PRODUCT(O128:Q128)</f>
+        <f t="shared" si="16"/>
         <v>1.5</v>
       </c>
       <c r="S128" s="75" t="str">
-        <f>IF(R128&gt;400,"Insustentável (risco extremo)", IF(R128&gt;200,"Significativo (risco muito alto)", IF(R128&gt;70,"Significativo (alto risco)", IF(R128&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T128" s="80" t="s">
@@ -33103,18 +33103,18 @@
         <v>0.2</v>
       </c>
       <c r="Z128" s="77">
-        <f>PRODUCT(W128:Y128)</f>
+        <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA128" s="75" t="str">
-        <f>IF(Z128&gt;400,"Insustentável (risco extremo)", IF(Z128&gt;200,"Significativo (risco muito alto)", IF(Z128&gt;70,"Significativo (alto risco)", IF(Z128&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB128" s="80" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="129" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A129" s="50">
         <v>176</v>
       </c>
@@ -33167,11 +33167,11 @@
         <v>3</v>
       </c>
       <c r="R129" s="74">
-        <f>PRODUCT(O129:Q129)</f>
+        <f t="shared" si="16"/>
         <v>54</v>
       </c>
       <c r="S129" s="75" t="str">
-        <f>IF(R129&gt;400,"Insustentável (risco extremo)", IF(R129&gt;200,"Significativo (risco muito alto)", IF(R129&gt;70,"Significativo (alto risco)", IF(R129&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T129" s="67" t="s">
@@ -33193,18 +33193,18 @@
         <v>0.1</v>
       </c>
       <c r="Z129" s="77">
-        <f>PRODUCT(W129:Y129)</f>
+        <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA129" s="75" t="str">
-        <f>IF(Z129&gt;400,"Insustentável (risco extremo)", IF(Z129&gt;200,"Significativo (risco muito alto)", IF(Z129&gt;70,"Significativo (alto risco)", IF(Z129&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB129" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="130" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="130" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A130" s="50">
         <v>178</v>
       </c>
@@ -33257,11 +33257,11 @@
         <v>0.5</v>
       </c>
       <c r="R130" s="74">
-        <f>PRODUCT(O130:Q130)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="S130" s="75" t="str">
-        <f>IF(R130&gt;400,"Insustentável (risco extremo)", IF(R130&gt;200,"Significativo (risco muito alto)", IF(R130&gt;70,"Significativo (alto risco)", IF(R130&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T130" s="67" t="s">
@@ -33283,18 +33283,18 @@
         <v>0.2</v>
       </c>
       <c r="Z130" s="77">
-        <f>PRODUCT(W130:Y130)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="AA130" s="75" t="str">
-        <f>IF(Z130&gt;400,"Insustentável (risco extremo)", IF(Z130&gt;200,"Significativo (risco muito alto)", IF(Z130&gt;70,"Significativo (alto risco)", IF(Z130&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB130" s="67" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="131" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A131" s="50">
         <v>179</v>
       </c>
@@ -33347,11 +33347,11 @@
         <v>1</v>
       </c>
       <c r="R131" s="74">
-        <f>PRODUCT(O131:Q131)</f>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="S131" s="75" t="str">
-        <f>IF(R131&gt;400,"Insustentável (risco extremo)", IF(R131&gt;200,"Significativo (risco muito alto)", IF(R131&gt;70,"Significativo (alto risco)", IF(R131&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T131" s="80" t="s">
@@ -33373,18 +33373,18 @@
         <v>0.5</v>
       </c>
       <c r="Z131" s="77">
-        <f>PRODUCT(W131:Y131)</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="AA131" s="75" t="str">
-        <f>IF(Z131&gt;400,"Insustentável (risco extremo)", IF(Z131&gt;200,"Significativo (risco muito alto)", IF(Z131&gt;70,"Significativo (alto risco)", IF(Z131&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB131" s="80" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="132" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="132" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A132" s="50">
         <v>180</v>
       </c>
@@ -33437,11 +33437,11 @@
         <v>1</v>
       </c>
       <c r="R132" s="74">
-        <f>PRODUCT(O132:Q132)</f>
+        <f t="shared" si="16"/>
         <v>90</v>
       </c>
       <c r="S132" s="75" t="str">
-        <f>IF(R132&gt;400,"Insustentável (risco extremo)", IF(R132&gt;200,"Significativo (risco muito alto)", IF(R132&gt;70,"Significativo (alto risco)", IF(R132&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (alto risco)</v>
       </c>
       <c r="T132" s="80" t="s">
@@ -33463,18 +33463,18 @@
         <v>0.5</v>
       </c>
       <c r="Z132" s="77">
-        <f>PRODUCT(W132:Y132)</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="AA132" s="75" t="str">
-        <f>IF(Z132&gt;400,"Insustentável (risco extremo)", IF(Z132&gt;200,"Significativo (risco muito alto)", IF(Z132&gt;70,"Significativo (alto risco)", IF(Z132&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB132" s="80" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="133" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="133" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A133" s="50">
         <v>182</v>
       </c>
@@ -33527,11 +33527,11 @@
         <v>0.5</v>
       </c>
       <c r="R133" s="74">
-        <f>PRODUCT(O133:Q133)</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="S133" s="75" t="str">
-        <f>IF(R133&gt;400,"Insustentável (risco extremo)", IF(R133&gt;200,"Significativo (risco muito alto)", IF(R133&gt;70,"Significativo (alto risco)", IF(R133&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T133" s="67" t="s">
@@ -33553,18 +33553,18 @@
         <v>0.2</v>
       </c>
       <c r="Z133" s="77">
-        <f>PRODUCT(W133:Y133)</f>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="AA133" s="75" t="str">
-        <f>IF(Z133&gt;400,"Insustentável (risco extremo)", IF(Z133&gt;200,"Significativo (risco muito alto)", IF(Z133&gt;70,"Significativo (alto risco)", IF(Z133&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB133" s="67" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="134" spans="1:28" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="134" spans="1:28" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A134" s="50"/>
       <c r="B134" s="78" t="s">
         <v>26</v>
@@ -33615,11 +33615,11 @@
         <v>0.5</v>
       </c>
       <c r="R134" s="74">
-        <f>PRODUCT(O134:Q134)</f>
+        <f t="shared" si="16"/>
         <v>3</v>
       </c>
       <c r="S134" s="75" t="str">
-        <f>IF(R134&gt;400,"Insustentável (risco extremo)", IF(R134&gt;200,"Significativo (risco muito alto)", IF(R134&gt;70,"Significativo (alto risco)", IF(R134&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T134" s="67" t="s">
@@ -33641,18 +33641,18 @@
         <v>0.2</v>
       </c>
       <c r="Z134" s="77">
-        <f>PRODUCT(W134:Y134)</f>
+        <f t="shared" si="15"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA134" s="75" t="str">
-        <f>IF(Z134&gt;400,"Insustentável (risco extremo)", IF(Z134&gt;200,"Significativo (risco muito alto)", IF(Z134&gt;70,"Significativo (alto risco)", IF(Z134&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB134" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="135" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="135" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A135" s="50">
         <v>183</v>
       </c>
@@ -33705,11 +33705,11 @@
         <v>0.5</v>
       </c>
       <c r="R135" s="74">
-        <f>PRODUCT(O135:Q135)</f>
+        <f t="shared" si="16"/>
         <v>7</v>
       </c>
       <c r="S135" s="75" t="str">
-        <f>IF(R135&gt;400,"Insustentável (risco extremo)", IF(R135&gt;200,"Significativo (risco muito alto)", IF(R135&gt;70,"Significativo (alto risco)", IF(R135&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T135" s="67" t="s">
@@ -33731,18 +33731,18 @@
         <v>0.2</v>
       </c>
       <c r="Z135" s="77">
-        <f>PRODUCT(W135:Y135)</f>
+        <f t="shared" si="15"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA135" s="75" t="str">
-        <f>IF(Z135&gt;400,"Insustentável (risco extremo)", IF(Z135&gt;200,"Significativo (risco muito alto)", IF(Z135&gt;70,"Significativo (alto risco)", IF(Z135&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB135" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="136" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="136" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A136" s="50">
         <v>184</v>
       </c>
@@ -33795,11 +33795,11 @@
         <v>0.5</v>
       </c>
       <c r="R136" s="74">
-        <f>PRODUCT(O136:Q136)</f>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="S136" s="75" t="str">
-        <f>IF(R136&gt;400,"Insustentável (risco extremo)", IF(R136&gt;200,"Significativo (risco muito alto)", IF(R136&gt;70,"Significativo (alto risco)", IF(R136&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T136" s="90" t="s">
@@ -33821,18 +33821,18 @@
         <v>0.1</v>
       </c>
       <c r="Z136" s="77">
-        <f>PRODUCT(W136:Y136)</f>
+        <f t="shared" si="15"/>
         <v>1.8</v>
       </c>
       <c r="AA136" s="75" t="str">
-        <f>IF(Z136&gt;400,"Insustentável (risco extremo)", IF(Z136&gt;200,"Significativo (risco muito alto)", IF(Z136&gt;70,"Significativo (alto risco)", IF(Z136&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB136" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="137" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A137" s="50">
         <v>185</v>
       </c>
@@ -33885,11 +33885,11 @@
         <v>0.5</v>
       </c>
       <c r="R137" s="74">
-        <f>PRODUCT(O137:Q137)</f>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="S137" s="75" t="str">
-        <f>IF(R137&gt;400,"Insustentável (risco extremo)", IF(R137&gt;200,"Significativo (risco muito alto)", IF(R137&gt;70,"Significativo (alto risco)", IF(R137&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T137" s="67" t="s">
@@ -33911,18 +33911,18 @@
         <v>0.1</v>
       </c>
       <c r="Z137" s="77">
-        <f>PRODUCT(W137:Y137)</f>
+        <f t="shared" si="15"/>
         <v>1.8</v>
       </c>
       <c r="AA137" s="75" t="str">
-        <f>IF(Z137&gt;400,"Insustentável (risco extremo)", IF(Z137&gt;200,"Significativo (risco muito alto)", IF(Z137&gt;70,"Significativo (alto risco)", IF(Z137&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB137" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="138" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="138" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A138" s="50">
         <v>186</v>
       </c>
@@ -33975,11 +33975,11 @@
         <v>0.5</v>
       </c>
       <c r="R138" s="74">
-        <f>PRODUCT(O138:Q138)</f>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="S138" s="75" t="str">
-        <f>IF(R138&gt;400,"Insustentável (risco extremo)", IF(R138&gt;200,"Significativo (risco muito alto)", IF(R138&gt;70,"Significativo (alto risco)", IF(R138&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T138" s="67" t="s">
@@ -34001,18 +34001,18 @@
         <v>0.1</v>
       </c>
       <c r="Z138" s="77">
-        <f>PRODUCT(W138:Y138)</f>
+        <f t="shared" si="15"/>
         <v>1.8</v>
       </c>
       <c r="AA138" s="75" t="str">
-        <f>IF(Z138&gt;400,"Insustentável (risco extremo)", IF(Z138&gt;200,"Significativo (risco muito alto)", IF(Z138&gt;70,"Significativo (alto risco)", IF(Z138&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB138" s="67" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="139" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="139" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A139" s="50">
         <v>188</v>
       </c>
@@ -34065,11 +34065,11 @@
         <v>0.2</v>
       </c>
       <c r="R139" s="74">
-        <f>PRODUCT(O139:Q139)</f>
+        <f t="shared" si="16"/>
         <v>1.2000000000000002</v>
       </c>
       <c r="S139" s="75" t="str">
-        <f>IF(R139&gt;400,"Insustentável (risco extremo)", IF(R139&gt;200,"Significativo (risco muito alto)", IF(R139&gt;70,"Significativo (alto risco)", IF(R139&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T139" s="67" t="s">
@@ -34091,11 +34091,11 @@
         <v>0.1</v>
       </c>
       <c r="Z139" s="77">
-        <f>PRODUCT(W139:Y139)</f>
+        <f t="shared" si="15"/>
         <v>0.60000000000000009</v>
       </c>
       <c r="AA139" s="75" t="str">
-        <f>IF(Z139&gt;400,"Insustentável (risco extremo)", IF(Z139&gt;200,"Significativo (risco muito alto)", IF(Z139&gt;70,"Significativo (alto risco)", IF(Z139&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB139" s="67" t="s">
@@ -34155,11 +34155,11 @@
         <v>0.5</v>
       </c>
       <c r="R140" s="74">
-        <f>PRODUCT(O140:Q140)</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="S140" s="75" t="str">
-        <f>IF(R140&gt;400,"Insustentável (risco extremo)", IF(R140&gt;200,"Significativo (risco muito alto)", IF(R140&gt;70,"Significativo (alto risco)", IF(R140&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T140" s="67" t="s">
@@ -34181,11 +34181,11 @@
         <v>0.2</v>
       </c>
       <c r="Z140" s="77">
-        <f>PRODUCT(W140:Y140)</f>
+        <f t="shared" si="15"/>
         <v>6</v>
       </c>
       <c r="AA140" s="75" t="str">
-        <f>IF(Z140&gt;400,"Insustentável (risco extremo)", IF(Z140&gt;200,"Significativo (risco muito alto)", IF(Z140&gt;70,"Significativo (alto risco)", IF(Z140&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB140" s="67" t="s">
@@ -34245,11 +34245,11 @@
         <v>3</v>
       </c>
       <c r="R141" s="74">
-        <f>PRODUCT(O141:Q141)</f>
+        <f t="shared" si="16"/>
         <v>450</v>
       </c>
       <c r="S141" s="75" t="str">
-        <f>IF(R141&gt;400,"Insustentável (risco extremo)", IF(R141&gt;200,"Significativo (risco muito alto)", IF(R141&gt;70,"Significativo (alto risco)", IF(R141&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insustentável (risco extremo)</v>
       </c>
       <c r="T141" s="67" t="s">
@@ -34271,11 +34271,11 @@
         <v>1</v>
       </c>
       <c r="Z141" s="77">
-        <f>PRODUCT(W141:Y141)</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="AA141" s="75" t="str">
-        <f>IF(Z141&gt;400,"Insustentável (risco extremo)", IF(Z141&gt;200,"Significativo (risco muito alto)", IF(Z141&gt;70,"Significativo (alto risco)", IF(Z141&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB141" s="67" t="s">
@@ -34333,11 +34333,11 @@
         <v>1</v>
       </c>
       <c r="R142" s="74">
-        <f>PRODUCT(O142:Q142)</f>
+        <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="S142" s="75" t="str">
-        <f>IF(R142&gt;400,"Insustentável (risco extremo)", IF(R142&gt;200,"Significativo (risco muito alto)", IF(R142&gt;70,"Significativo (alto risco)", IF(R142&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T142" s="67" t="s">
@@ -34359,11 +34359,11 @@
         <v>0.5</v>
       </c>
       <c r="Z142" s="77">
-        <f>PRODUCT(W142:Y142)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="AA142" s="75" t="str">
-        <f>IF(Z142&gt;400,"Insustentável (risco extremo)", IF(Z142&gt;200,"Significativo (risco muito alto)", IF(Z142&gt;70,"Significativo (alto risco)", IF(Z142&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB142" s="67" t="s">
@@ -34423,11 +34423,11 @@
         <v>1</v>
       </c>
       <c r="R143" s="74">
-        <f>PRODUCT(O143:Q143)</f>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="S143" s="75" t="str">
-        <f>IF(R143&gt;400,"Insustentável (risco extremo)", IF(R143&gt;200,"Significativo (risco muito alto)", IF(R143&gt;70,"Significativo (alto risco)", IF(R143&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T143" s="67" t="s">
@@ -34449,11 +34449,11 @@
         <v>0.5</v>
       </c>
       <c r="Z143" s="77">
-        <f>PRODUCT(W143:Y143)</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="AA143" s="75" t="str">
-        <f>IF(Z143&gt;400,"Insustentável (risco extremo)", IF(Z143&gt;200,"Significativo (risco muito alto)", IF(Z143&gt;70,"Significativo (alto risco)", IF(Z143&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB143" s="67" t="s">
@@ -34513,11 +34513,11 @@
         <v>1</v>
       </c>
       <c r="R144" s="74">
-        <f>PRODUCT(O144:Q144)</f>
+        <f t="shared" si="16"/>
         <v>18</v>
       </c>
       <c r="S144" s="75" t="str">
-        <f>IF(R144&gt;400,"Insustentável (risco extremo)", IF(R144&gt;200,"Significativo (risco muito alto)", IF(R144&gt;70,"Significativo (alto risco)", IF(R144&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T144" s="67" t="s">
@@ -34539,11 +34539,11 @@
         <v>0.5</v>
       </c>
       <c r="Z144" s="77">
-        <f>PRODUCT(W144:Y144)</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="AA144" s="75" t="str">
-        <f>IF(Z144&gt;400,"Insustentável (risco extremo)", IF(Z144&gt;200,"Significativo (risco muito alto)", IF(Z144&gt;70,"Significativo (alto risco)", IF(Z144&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB144" s="67" t="s">
@@ -34603,11 +34603,11 @@
         <v>0.5</v>
       </c>
       <c r="R145" s="74">
-        <f>PRODUCT(O145:Q145)</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="S145" s="75" t="str">
-        <f>IF(R145&gt;400,"Insustentável (risco extremo)", IF(R145&gt;200,"Significativo (risco muito alto)", IF(R145&gt;70,"Significativo (alto risco)", IF(R145&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T145" s="67" t="s">
@@ -34629,11 +34629,11 @@
         <v>0.2</v>
       </c>
       <c r="Z145" s="77">
-        <f>PRODUCT(W145:Y145)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="AA145" s="75" t="str">
-        <f>IF(Z145&gt;400,"Insustentável (risco extremo)", IF(Z145&gt;200,"Significativo (risco muito alto)", IF(Z145&gt;70,"Significativo (alto risco)", IF(Z145&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB145" s="67" t="s">
@@ -34694,11 +34694,11 @@
         <v>0.5</v>
       </c>
       <c r="R146" s="74">
-        <f>PRODUCT(O146:Q146)</f>
+        <f t="shared" si="16"/>
         <v>4.5</v>
       </c>
       <c r="S146" s="75" t="str">
-        <f>IF(R146&gt;400,"Insustentável (risco extremo)", IF(R146&gt;200,"Significativo (risco muito alto)", IF(R146&gt;70,"Significativo (alto risco)", IF(R146&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T146" s="67" t="s">
@@ -34720,11 +34720,11 @@
         <v>0.5</v>
       </c>
       <c r="Z146" s="77">
-        <f>PRODUCT(W146:Y146)</f>
+        <f t="shared" si="15"/>
         <v>1.5</v>
       </c>
       <c r="AA146" s="75" t="str">
-        <f>IF(Z146&gt;400,"Insustentável (risco extremo)", IF(Z146&gt;200,"Significativo (risco muito alto)", IF(Z146&gt;70,"Significativo (alto risco)", IF(Z146&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB146" s="67" t="s">
@@ -34785,11 +34785,11 @@
         <v>0.5</v>
       </c>
       <c r="R147" s="74">
-        <f>PRODUCT(O147:Q147)</f>
+        <f t="shared" si="16"/>
         <v>15</v>
       </c>
       <c r="S147" s="75" t="str">
-        <f>IF(R147&gt;400,"Insustentável (risco extremo)", IF(R147&gt;200,"Significativo (risco muito alto)", IF(R147&gt;70,"Significativo (alto risco)", IF(R147&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T147" s="67" t="s">
@@ -34811,11 +34811,11 @@
         <v>0.2</v>
       </c>
       <c r="Z147" s="77">
-        <f>PRODUCT(W147:Y147)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="AA147" s="75" t="str">
-        <f>IF(Z147&gt;400,"Insustentável (risco extremo)", IF(Z147&gt;200,"Significativo (risco muito alto)", IF(Z147&gt;70,"Significativo (alto risco)", IF(Z147&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB147" s="67" t="s">
@@ -34876,11 +34876,11 @@
         <v>1</v>
       </c>
       <c r="R148" s="74">
-        <f>PRODUCT(O148:Q148)</f>
+        <f t="shared" si="16"/>
         <v>30</v>
       </c>
       <c r="S148" s="75" t="str">
-        <f>IF(R148&gt;400,"Insustentável (risco extremo)", IF(R148&gt;200,"Significativo (risco muito alto)", IF(R148&gt;70,"Significativo (alto risco)", IF(R148&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T148" s="67" t="s">
@@ -34902,11 +34902,11 @@
         <v>0.5</v>
       </c>
       <c r="Z148" s="77">
-        <f>PRODUCT(W148:Y148)</f>
+        <f t="shared" si="15"/>
         <v>15</v>
       </c>
       <c r="AA148" s="75" t="str">
-        <f>IF(Z148&gt;400,"Insustentável (risco extremo)", IF(Z148&gt;200,"Significativo (risco muito alto)", IF(Z148&gt;70,"Significativo (alto risco)", IF(Z148&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB148" s="67" t="s">
@@ -34965,11 +34965,11 @@
         <v>6</v>
       </c>
       <c r="R149" s="74">
-        <f>PRODUCT(O149:Q149)</f>
+        <f t="shared" si="16"/>
         <v>420</v>
       </c>
       <c r="S149" s="75" t="str">
-        <f>IF(R149&gt;400,"Insustentável (risco extremo)", IF(R149&gt;200,"Significativo (risco muito alto)", IF(R149&gt;70,"Significativo (alto risco)", IF(R149&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insustentável (risco extremo)</v>
       </c>
       <c r="T149" s="67" t="s">
@@ -34991,11 +34991,11 @@
         <v>1</v>
       </c>
       <c r="Z149" s="77">
-        <f>PRODUCT(W149:Y149)</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="AA149" s="75" t="str">
-        <f>IF(Z149&gt;400,"Insustentável (risco extremo)", IF(Z149&gt;200,"Significativo (risco muito alto)", IF(Z149&gt;70,"Significativo (alto risco)", IF(Z149&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB149" s="67" t="s">
@@ -35056,11 +35056,11 @@
         <v>1</v>
       </c>
       <c r="R150" s="74">
-        <f>PRODUCT(O150:Q150)</f>
+        <f t="shared" si="16"/>
         <v>70</v>
       </c>
       <c r="S150" s="75" t="str">
-        <f>IF(R150&gt;400,"Insustentável (risco extremo)", IF(R150&gt;200,"Significativo (risco muito alto)", IF(R150&gt;70,"Significativo (alto risco)", IF(R150&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T150" s="67" t="s">
@@ -35082,11 +35082,11 @@
         <v>1</v>
       </c>
       <c r="Z150" s="77">
-        <f>PRODUCT(W150:Y150)</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="AA150" s="75" t="str">
-        <f>IF(Z150&gt;400,"Insustentável (risco extremo)", IF(Z150&gt;200,"Significativo (risco muito alto)", IF(Z150&gt;70,"Significativo (alto risco)", IF(Z150&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB150" s="67" t="s">
@@ -35147,11 +35147,11 @@
         <v>1</v>
       </c>
       <c r="R151" s="74">
-        <f>PRODUCT(O151:Q151)</f>
+        <f t="shared" si="16"/>
         <v>70</v>
       </c>
       <c r="S151" s="75" t="str">
-        <f>IF(R151&gt;400,"Insustentável (risco extremo)", IF(R151&gt;200,"Significativo (risco muito alto)", IF(R151&gt;70,"Significativo (alto risco)", IF(R151&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="T151" s="67" t="s">
@@ -35173,11 +35173,11 @@
         <v>1</v>
       </c>
       <c r="Z151" s="77">
-        <f>PRODUCT(W151:Y151)</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="AA151" s="75" t="str">
-        <f>IF(Z151&gt;400,"Insustentável (risco extremo)", IF(Z151&gt;200,"Significativo (risco muito alto)", IF(Z151&gt;70,"Significativo (alto risco)", IF(Z151&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB151" s="67" t="s">
@@ -35238,11 +35238,11 @@
         <v>1</v>
       </c>
       <c r="R152" s="74">
-        <f>PRODUCT(O152:Q152)</f>
+        <f t="shared" si="16"/>
         <v>400</v>
       </c>
       <c r="S152" s="75" t="str">
-        <f>IF(R152&gt;400,"Insustentável (risco extremo)", IF(R152&gt;200,"Significativo (risco muito alto)", IF(R152&gt;70,"Significativo (alto risco)", IF(R152&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco muito alto)</v>
       </c>
       <c r="T152" s="67" t="s">
@@ -35264,11 +35264,11 @@
         <v>1</v>
       </c>
       <c r="Z152" s="77">
-        <f>PRODUCT(W152:Y152)</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="AA152" s="75" t="str">
-        <f>IF(Z152&gt;400,"Insustentável (risco extremo)", IF(Z152&gt;200,"Significativo (risco muito alto)", IF(Z152&gt;70,"Significativo (alto risco)", IF(Z152&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB152" s="67" t="s">
@@ -35329,11 +35329,11 @@
         <v>0.5</v>
       </c>
       <c r="R153" s="74">
-        <f>PRODUCT(O153:Q153)</f>
+        <f t="shared" si="16"/>
         <v>5</v>
       </c>
       <c r="S153" s="75" t="str">
-        <f>IF(R153&gt;400,"Insustentável (risco extremo)", IF(R153&gt;200,"Significativo (risco muito alto)", IF(R153&gt;70,"Significativo (alto risco)", IF(R153&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T153" s="67" t="s">
@@ -35355,11 +35355,11 @@
         <v>0.2</v>
       </c>
       <c r="Z153" s="77">
-        <f>PRODUCT(W153:Y153)</f>
+        <f t="shared" si="15"/>
         <v>2</v>
       </c>
       <c r="AA153" s="75" t="str">
-        <f>IF(Z153&gt;400,"Insustentável (risco extremo)", IF(Z153&gt;200,"Significativo (risco muito alto)", IF(Z153&gt;70,"Significativo (alto risco)", IF(Z153&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB153" s="80" t="s">
@@ -35420,11 +35420,11 @@
         <v>10</v>
       </c>
       <c r="R154" s="74">
-        <f>PRODUCT(O154:Q154)</f>
+        <f t="shared" si="16"/>
         <v>1200</v>
       </c>
       <c r="S154" s="75" t="str">
-        <f>IF(R154&gt;400,"Insustentável (risco extremo)", IF(R154&gt;200,"Significativo (risco muito alto)", IF(R154&gt;70,"Significativo (alto risco)", IF(R154&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insustentável (risco extremo)</v>
       </c>
       <c r="T154" s="67" t="s">
@@ -35446,11 +35446,11 @@
         <v>1</v>
       </c>
       <c r="Z154" s="77">
-        <f>PRODUCT(W154:Y154)</f>
+        <f t="shared" si="15"/>
         <v>9</v>
       </c>
       <c r="AA154" s="75" t="str">
-        <f>IF(Z154&gt;400,"Insustentável (risco extremo)", IF(Z154&gt;200,"Significativo (risco muito alto)", IF(Z154&gt;70,"Significativo (alto risco)", IF(Z154&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB154" s="67" t="s">
@@ -35508,11 +35508,11 @@
         <v>1</v>
       </c>
       <c r="R155" s="82">
-        <f>PRODUCT(O155:Q155)</f>
+        <f t="shared" si="16"/>
         <v>9</v>
       </c>
       <c r="S155" s="75" t="str">
-        <f>IF(R155&gt;400,"Insustentável (risco extremo)", IF(R155&gt;200,"Significativo (risco muito alto)", IF(R155&gt;70,"Significativo (alto risco)", IF(R155&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Insignificante</v>
       </c>
       <c r="T155" s="67" t="s">
@@ -35534,11 +35534,11 @@
         <v>0.5</v>
       </c>
       <c r="Z155" s="77">
-        <f>PRODUCT(W155:Y155)</f>
+        <f t="shared" si="15"/>
         <v>4.5</v>
       </c>
       <c r="AA155" s="75" t="str">
-        <f>IF(Z155&gt;400,"Insustentável (risco extremo)", IF(Z155&gt;200,"Significativo (risco muito alto)", IF(Z155&gt;70,"Significativo (alto risco)", IF(Z155&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Insignificante</v>
       </c>
       <c r="AB155" s="80" t="s">
@@ -35550,7 +35550,7 @@
         <v>26</v>
       </c>
       <c r="C156" s="67" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="D156" s="67" t="s">
         <v>28</v>
@@ -35595,11 +35595,11 @@
         <v>3</v>
       </c>
       <c r="R156" s="74">
-        <f>PRODUCT(O156:Q156)</f>
+        <f t="shared" si="16"/>
         <v>210</v>
       </c>
       <c r="S156" s="75" t="str">
-        <f>IF(R156&gt;400,"Insustentável (risco extremo)", IF(R156&gt;200,"Significativo (risco muito alto)", IF(R156&gt;70,"Significativo (alto risco)", IF(R156&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="17"/>
         <v>Significativo (risco muito alto)</v>
       </c>
       <c r="T156" s="67" t="s">
@@ -35621,11 +35621,11 @@
         <v>1</v>
       </c>
       <c r="Z156" s="77">
-        <f>PRODUCT(W156:Y156)</f>
+        <f t="shared" si="15"/>
         <v>30</v>
       </c>
       <c r="AA156" s="75" t="str">
-        <f>IF(Z156&gt;400,"Insustentável (risco extremo)", IF(Z156&gt;200,"Significativo (risco muito alto)", IF(Z156&gt;70,"Significativo (alto risco)", IF(Z156&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" si="18"/>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB156" s="67" t="s">
@@ -35638,6 +35638,12 @@
     </row>
   </sheetData>
   <autoFilter ref="B3:AB156" xr:uid="{F9A4741E-2134-4562-B632-CA537B03EF9D}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Torrefação"/>
+        <filter val="Torrefação, Moagem, Café Cru"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:AB156">
       <sortCondition ref="C3:C156"/>
     </sortState>
@@ -37134,47 +37140,47 @@
     <row r="1" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:20" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="139" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="112"/>
-      <c r="D2" s="113"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="140"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="114" t="s">
+      <c r="F2" s="141" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="115"/>
-      <c r="H2" s="115"/>
-      <c r="I2" s="115"/>
-      <c r="J2" s="115"/>
-      <c r="K2" s="115"/>
-      <c r="L2" s="115"/>
-      <c r="M2" s="115"/>
-      <c r="N2" s="115"/>
-      <c r="O2" s="115"/>
-      <c r="P2" s="115"/>
-      <c r="Q2" s="115"/>
-      <c r="R2" s="115"/>
-      <c r="S2" s="115"/>
-      <c r="T2" s="116"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="142"/>
+      <c r="R2" s="142"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="143"/>
     </row>
     <row r="3" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="117"/>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-      <c r="K3" s="117"/>
-      <c r="L3" s="117"/>
-      <c r="M3" s="117"/>
-      <c r="N3" s="117"/>
-      <c r="O3" s="117"/>
-      <c r="P3" s="117"/>
-      <c r="Q3" s="117"/>
+      <c r="B3" s="123"/>
+      <c r="C3" s="123"/>
+      <c r="D3" s="123"/>
+      <c r="E3" s="123"/>
+      <c r="F3" s="123"/>
+      <c r="G3" s="123"/>
+      <c r="H3" s="123"/>
+      <c r="I3" s="123"/>
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="123"/>
+      <c r="P3" s="123"/>
+      <c r="Q3" s="123"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -37193,10 +37199,10 @@
       <c r="H4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="118" t="s">
+      <c r="J4" s="144" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="119"/>
+      <c r="K4" s="145"/>
       <c r="M4" s="7">
         <f>IF(M18=6,H16,IF(M18=5,H14,IF(M18=4,H12,IF(M18=3,H10,IF(M18=2,H8,IF(M18=1,H6,""))))))</f>
         <v>10</v>
@@ -37579,27 +37585,27 @@
       <c r="T23" s="11"/>
     </row>
     <row r="24" spans="2:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="146" t="s">
         <v>243</v>
       </c>
-      <c r="C24" s="121"/>
-      <c r="D24" s="122"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="148"/>
       <c r="F24" s="26" t="e">
         <f>(F4*M4)*S4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H24" s="123" t="s">
+      <c r="H24" s="149" t="s">
         <v>244</v>
       </c>
-      <c r="I24" s="121"/>
-      <c r="J24" s="121"/>
-      <c r="K24" s="121"/>
-      <c r="L24" s="121"/>
-      <c r="M24" s="121"/>
-      <c r="N24" s="121"/>
-      <c r="O24" s="121"/>
-      <c r="P24" s="121"/>
-      <c r="Q24" s="122"/>
+      <c r="I24" s="147"/>
+      <c r="J24" s="147"/>
+      <c r="K24" s="147"/>
+      <c r="L24" s="147"/>
+      <c r="M24" s="147"/>
+      <c r="N24" s="147"/>
+      <c r="O24" s="147"/>
+      <c r="P24" s="147"/>
+      <c r="Q24" s="148"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -37610,27 +37616,27 @@
       <c r="D25" s="27"/>
     </row>
     <row r="26" spans="2:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B26" s="130" t="s">
+      <c r="B26" s="124" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="131"/>
-      <c r="D26" s="132"/>
+      <c r="C26" s="125"/>
+      <c r="D26" s="126"/>
       <c r="F26" s="28" t="e">
         <f>IF($F$24&gt;=400,"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H26" s="133" t="s">
+      <c r="H26" s="127" t="s">
         <v>246</v>
       </c>
-      <c r="I26" s="134"/>
-      <c r="J26" s="134"/>
-      <c r="K26" s="134"/>
-      <c r="L26" s="134"/>
-      <c r="M26" s="134"/>
-      <c r="N26" s="134"/>
-      <c r="O26" s="134"/>
-      <c r="P26" s="134"/>
-      <c r="Q26" s="135"/>
+      <c r="I26" s="128"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="128"/>
+      <c r="N26" s="128"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="128"/>
+      <c r="Q26" s="129"/>
       <c r="R26" s="1"/>
       <c r="S26" s="28" t="e">
         <f>IF($F$24&gt;=400,"&lt;","")</f>
@@ -37658,23 +37664,23 @@
       <c r="T27" s="1"/>
     </row>
     <row r="28" spans="2:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="142" t="s">
+      <c r="B28" s="136" t="s">
         <v>247</v>
       </c>
-      <c r="C28" s="143"/>
-      <c r="D28" s="144"/>
-      <c r="H28" s="133" t="s">
+      <c r="C28" s="137"/>
+      <c r="D28" s="138"/>
+      <c r="H28" s="127" t="s">
         <v>248</v>
       </c>
-      <c r="I28" s="134"/>
-      <c r="J28" s="134"/>
-      <c r="K28" s="134"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="134"/>
-      <c r="N28" s="134"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="134"/>
-      <c r="Q28" s="135"/>
+      <c r="I28" s="128"/>
+      <c r="J28" s="128"/>
+      <c r="K28" s="128"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="128"/>
+      <c r="N28" s="128"/>
+      <c r="O28" s="128"/>
+      <c r="P28" s="128"/>
+      <c r="Q28" s="129"/>
     </row>
     <row r="29" spans="2:20" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="27"/>
@@ -37692,27 +37698,27 @@
       <c r="Q29" s="27"/>
     </row>
     <row r="30" spans="2:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B30" s="136" t="s">
+      <c r="B30" s="130" t="s">
         <v>249</v>
       </c>
-      <c r="C30" s="137"/>
-      <c r="D30" s="138"/>
+      <c r="C30" s="131"/>
+      <c r="D30" s="132"/>
       <c r="F30" s="28" t="e">
         <f>IF(AND($F24&lt;400,$F$24&gt;=200),"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="127" t="s">
+      <c r="H30" s="120" t="s">
         <v>250</v>
       </c>
-      <c r="I30" s="128"/>
-      <c r="J30" s="128"/>
-      <c r="K30" s="128"/>
-      <c r="L30" s="128"/>
-      <c r="M30" s="128"/>
-      <c r="N30" s="128"/>
-      <c r="O30" s="128"/>
-      <c r="P30" s="128"/>
-      <c r="Q30" s="129"/>
+      <c r="I30" s="121"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="121"/>
+      <c r="L30" s="121"/>
+      <c r="M30" s="121"/>
+      <c r="N30" s="121"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="122"/>
       <c r="R30" s="1"/>
       <c r="S30" s="28" t="e">
         <f>IF(AND($F24&lt;400,$F$24&gt;=200),"&lt;","")</f>
@@ -37736,27 +37742,27 @@
       <c r="Q31" s="27"/>
     </row>
     <row r="32" spans="2:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B32" s="139" t="s">
+      <c r="B32" s="133" t="s">
         <v>251</v>
       </c>
-      <c r="C32" s="140"/>
-      <c r="D32" s="141"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="135"/>
       <c r="F32" s="28" t="e">
         <f>IF(AND($F$24&lt;200,$F$24&gt;=70),"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="127" t="s">
+      <c r="H32" s="120" t="s">
         <v>252</v>
       </c>
-      <c r="I32" s="128"/>
-      <c r="J32" s="128"/>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-      <c r="M32" s="128"/>
-      <c r="N32" s="128"/>
-      <c r="O32" s="128"/>
-      <c r="P32" s="128"/>
-      <c r="Q32" s="129"/>
+      <c r="I32" s="121"/>
+      <c r="J32" s="121"/>
+      <c r="K32" s="121"/>
+      <c r="L32" s="121"/>
+      <c r="M32" s="121"/>
+      <c r="N32" s="121"/>
+      <c r="O32" s="121"/>
+      <c r="P32" s="121"/>
+      <c r="Q32" s="122"/>
       <c r="R32" s="1"/>
       <c r="S32" s="28" t="e">
         <f>IF(AND($F$24&lt;200,$F$24&gt;=70),"&lt;","")</f>
@@ -37795,27 +37801,27 @@
       <c r="Q34" s="27"/>
     </row>
     <row r="35" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B35" s="124" t="s">
+      <c r="B35" s="117" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="125"/>
-      <c r="D35" s="126"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="119"/>
       <c r="F35" s="28" t="e">
         <f>IF($F$24&lt;20,"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H35" s="127" t="s">
+      <c r="H35" s="120" t="s">
         <v>254</v>
       </c>
-      <c r="I35" s="128"/>
-      <c r="J35" s="128"/>
-      <c r="K35" s="128"/>
-      <c r="L35" s="128"/>
-      <c r="M35" s="128"/>
-      <c r="N35" s="128"/>
-      <c r="O35" s="128"/>
-      <c r="P35" s="128"/>
-      <c r="Q35" s="129"/>
+      <c r="I35" s="121"/>
+      <c r="J35" s="121"/>
+      <c r="K35" s="121"/>
+      <c r="L35" s="121"/>
+      <c r="M35" s="121"/>
+      <c r="N35" s="121"/>
+      <c r="O35" s="121"/>
+      <c r="P35" s="121"/>
+      <c r="Q35" s="122"/>
       <c r="R35" s="1"/>
       <c r="S35" s="28" t="e">
         <f>IF($F$24&lt;20,"&lt;","")</f>
@@ -37825,22 +37831,22 @@
     </row>
     <row r="36" spans="2:20" ht="5.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="2:20" ht="12.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="117"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="117"/>
-      <c r="E37" s="117"/>
-      <c r="F37" s="117"/>
-      <c r="G37" s="117"/>
-      <c r="H37" s="117"/>
-      <c r="I37" s="117"/>
-      <c r="J37" s="117"/>
-      <c r="K37" s="117"/>
-      <c r="L37" s="117"/>
-      <c r="M37" s="117"/>
-      <c r="N37" s="117"/>
-      <c r="O37" s="117"/>
-      <c r="P37" s="117"/>
-      <c r="Q37" s="117"/>
+      <c r="B37" s="123"/>
+      <c r="C37" s="123"/>
+      <c r="D37" s="123"/>
+      <c r="E37" s="123"/>
+      <c r="F37" s="123"/>
+      <c r="G37" s="123"/>
+      <c r="H37" s="123"/>
+      <c r="I37" s="123"/>
+      <c r="J37" s="123"/>
+      <c r="K37" s="123"/>
+      <c r="L37" s="123"/>
+      <c r="M37" s="123"/>
+      <c r="N37" s="123"/>
+      <c r="O37" s="123"/>
+      <c r="P37" s="123"/>
+      <c r="Q37" s="123"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
@@ -37860,6 +37866,12 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="17">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:T2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="H24:Q24"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="H35:Q35"/>
     <mergeCell ref="B37:Q37"/>
@@ -37871,12 +37883,6 @@
     <mergeCell ref="H32:Q32"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="H28:Q28"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:T2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="H24:Q24"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.9055118110236221" right="0.74803149606299213" top="0.74803149606299213" bottom="0.6692913385826772" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -39280,20 +39286,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ee15a44e-0948-420d-96df-d16ce70ffded" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ee15a44e-0948-420d-96df-d16ce70ffded" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -39316,14 +39322,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE14A1C-5FB1-4FE4-BBAD-C2D265A18624}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FD52C5A-C1F0-4A58-ABE1-434C0069F4B0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="ee15a44e-0948-420d-96df-d16ce70ffded"/>
@@ -39338,4 +39336,12 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE14A1C-5FB1-4FE4-BBAD-C2D265A18624}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/dados/LAIA.xlsx
+++ b/dados/LAIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samuel.camargo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA3049E-43B8-4CAE-8CB1-D6B514F10CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF97FFBB-4898-49B8-A80C-735EA81B3CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2958,6 +2958,42 @@
     <xf numFmtId="0" fontId="48" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2975,9 +3011,6 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3023,39 +3056,6 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3353,7 +3353,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[PIU - LAIA.xlsx]Significância-processo-aspecto!Tabela dinâmica3</c:name>
+    <c:name>[LAIA.xlsx]Significância-processo-aspecto!Tabela dinâmica3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -24812,7 +24812,7 @@
         <v>270</v>
       </c>
       <c r="S36" s="75" t="str">
-        <f t="shared" ref="S36:S67" si="5">IF(R36&gt;400,"Insustentável (risco extremo)", IF(R36&gt;200,"Significativo (risco muito alto)", IF(R36&gt;70,"Significativo (alto risco)", IF(R36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="S36:S59" si="5">IF(R36&gt;400,"Insustentável (risco extremo)", IF(R36&gt;200,"Significativo (risco muito alto)", IF(R36&gt;70,"Significativo (alto risco)", IF(R36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Significativo (risco muito alto)</v>
       </c>
       <c r="T36" s="67" t="s">
@@ -24838,7 +24838,7 @@
         <v>54</v>
       </c>
       <c r="AA36" s="75" t="str">
-        <f t="shared" ref="AA36:AA67" si="6">IF(Z36&gt;400,"Insustentável (risco extremo)", IF(Z36&gt;200,"Significativo (risco muito alto)", IF(Z36&gt;70,"Significativo (alto risco)", IF(Z36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
+        <f t="shared" ref="AA36:AA59" si="6">IF(Z36&gt;400,"Insustentável (risco extremo)", IF(Z36&gt;200,"Significativo (risco muito alto)", IF(Z36&gt;70,"Significativo (alto risco)", IF(Z36&gt;21,"Significativo (risco médio)", "Insignificante"))))</f>
         <v>Significativo (risco médio)</v>
       </c>
       <c r="AB36" s="67" t="s">
@@ -25882,18 +25882,18 @@
         <v>3</v>
       </c>
       <c r="P48" s="72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q48" s="73">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R48" s="74">
         <f t="shared" si="3"/>
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="S48" s="75" t="str">
         <f t="shared" si="5"/>
-        <v>Significativo (alto risco)</v>
+        <v>Significativo (risco médio)</v>
       </c>
       <c r="T48" s="67" t="s">
         <v>296</v>
@@ -25905,17 +25905,17 @@
         <v>298</v>
       </c>
       <c r="W48" s="76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X48" s="72">
         <v>3</v>
       </c>
       <c r="Y48" s="73">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Z48" s="77">
         <f t="shared" si="4"/>
-        <v>0.30000000000000004</v>
+        <v>9</v>
       </c>
       <c r="AA48" s="75" t="str">
         <f t="shared" si="6"/>
@@ -26150,14 +26150,14 @@
         <v>2</v>
       </c>
       <c r="P51" s="72">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q51" s="73">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="R51" s="74">
         <f t="shared" si="3"/>
-        <v>1.4000000000000001</v>
+        <v>6</v>
       </c>
       <c r="S51" s="75" t="str">
         <f t="shared" si="5"/>
@@ -26179,11 +26179,11 @@
         <v>3</v>
       </c>
       <c r="Y51" s="73">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Z51" s="77">
         <f t="shared" si="4"/>
-        <v>0.60000000000000009</v>
+        <v>3</v>
       </c>
       <c r="AA51" s="75" t="str">
         <f t="shared" si="6"/>
@@ -26283,7 +26283,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="53" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="53" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A53" s="50">
         <v>67</v>
       </c>
@@ -26327,17 +26327,17 @@
         <v>33</v>
       </c>
       <c r="O53" s="71">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P53" s="72">
         <v>3</v>
       </c>
       <c r="Q53" s="73">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R53" s="74">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="S53" s="75" t="str">
         <f t="shared" si="5"/>
@@ -26359,11 +26359,11 @@
         <v>3</v>
       </c>
       <c r="Y53" s="73">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Z53" s="77">
         <f t="shared" si="4"/>
-        <v>0.60000000000000009</v>
+        <v>3</v>
       </c>
       <c r="AA53" s="75" t="str">
         <f t="shared" si="6"/>
@@ -26373,7 +26373,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" customHeight="1" x14ac:dyDescent="1.45">
+    <row r="54" spans="1:28" s="54" customFormat="1" ht="382.5" customHeight="1" x14ac:dyDescent="1.45">
       <c r="A54" s="50">
         <v>69</v>
       </c>
@@ -26417,17 +26417,17 @@
         <v>43</v>
       </c>
       <c r="O54" s="71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P54" s="72">
         <v>3</v>
       </c>
       <c r="Q54" s="73">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R54" s="74">
         <f t="shared" si="3"/>
-        <v>1.2000000000000002</v>
+        <v>9</v>
       </c>
       <c r="S54" s="75" t="str">
         <f t="shared" si="5"/>
@@ -26449,11 +26449,11 @@
         <v>3</v>
       </c>
       <c r="Y54" s="73">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="Z54" s="77">
         <f t="shared" si="4"/>
-        <v>0.60000000000000009</v>
+        <v>3</v>
       </c>
       <c r="AA54" s="75" t="str">
         <f t="shared" si="6"/>
@@ -26463,7 +26463,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="55" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A55" s="50">
         <v>70</v>
       </c>
@@ -26507,7 +26507,7 @@
         <v>35</v>
       </c>
       <c r="O55" s="71">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P55" s="72">
         <v>3</v>
@@ -26517,7 +26517,7 @@
       </c>
       <c r="R55" s="74">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="S55" s="75" t="str">
         <f t="shared" si="5"/>
@@ -26553,7 +26553,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="56" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="56" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A56" s="50">
         <v>72</v>
       </c>
@@ -26643,7 +26643,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="57" spans="1:28" s="54" customFormat="1" ht="409.5" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A57" s="50">
         <v>73</v>
       </c>
@@ -26690,14 +26690,14 @@
         <v>10</v>
       </c>
       <c r="P57" s="72">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q57" s="73">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="R57" s="74">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="S57" s="75" t="str">
         <f t="shared" si="5"/>
@@ -26733,7 +26733,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="58" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="58" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A58" s="50">
         <v>74</v>
       </c>
@@ -26823,7 +26823,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="59" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="59" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A59" s="50">
         <v>75</v>
       </c>
@@ -26913,7 +26913,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="60" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A60" s="50">
         <v>76</v>
       </c>
@@ -26999,7 +26999,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="61" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="61" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A61" s="50">
         <v>77</v>
       </c>
@@ -27089,7 +27089,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="62" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="62" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A62" s="50">
         <v>78</v>
       </c>
@@ -27179,7 +27179,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="63" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="63" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
       <c r="A63" s="50">
         <v>79</v>
       </c>
@@ -29956,7 +29956,7 @@
         <v>0.2</v>
       </c>
       <c r="Z93" s="77">
-        <f t="shared" ref="Z93:Z124" si="13">PRODUCT(W93:Y93)</f>
+        <f t="shared" ref="Z93:Z119" si="13">PRODUCT(W93:Y93)</f>
         <v>1.2000000000000002</v>
       </c>
       <c r="AA93" s="75" t="str">
@@ -34102,7 +34102,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="140" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="140" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A140" s="50">
         <v>190</v>
       </c>
@@ -34192,7 +34192,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="141" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="141" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A141" s="50">
         <v>192</v>
       </c>
@@ -34282,7 +34282,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="142" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="142" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A142" s="50"/>
       <c r="B142" s="81" t="s">
         <v>26</v>
@@ -34370,7 +34370,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="143" spans="1:28" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="143" spans="1:28" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A143" s="50">
         <v>193</v>
       </c>
@@ -34460,7 +34460,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" spans="1:28" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="144" spans="1:28" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A144" s="50">
         <v>197</v>
       </c>
@@ -34550,7 +34550,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="145" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="145" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A145" s="53">
         <v>201</v>
       </c>
@@ -34641,7 +34641,7 @@
       </c>
       <c r="AC145" s="59"/>
     </row>
-    <row r="146" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="146" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A146" s="53">
         <v>202</v>
       </c>
@@ -34732,7 +34732,7 @@
       </c>
       <c r="AC146" s="59"/>
     </row>
-    <row r="147" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="147" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A147" s="53">
         <v>203</v>
       </c>
@@ -34823,7 +34823,7 @@
       </c>
       <c r="AC147" s="59"/>
     </row>
-    <row r="148" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="148" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A148" s="53">
         <v>205</v>
       </c>
@@ -34914,7 +34914,7 @@
       </c>
       <c r="AC148" s="59"/>
     </row>
-    <row r="149" spans="1:29" s="54" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="149" spans="1:29" s="54" customFormat="1" ht="409.6" hidden="1" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A149" s="53"/>
       <c r="B149" s="81" t="s">
         <v>26</v>
@@ -35003,7 +35003,7 @@
       </c>
       <c r="AC149" s="59"/>
     </row>
-    <row r="150" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="150" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A150" s="53">
         <v>208</v>
       </c>
@@ -35094,7 +35094,7 @@
       </c>
       <c r="AC150" s="59"/>
     </row>
-    <row r="151" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="151" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A151" s="53">
         <v>209</v>
       </c>
@@ -35185,7 +35185,7 @@
       </c>
       <c r="AC151" s="59"/>
     </row>
-    <row r="152" spans="1:29" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="152" spans="1:29" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A152" s="53">
         <v>210</v>
       </c>
@@ -35276,7 +35276,7 @@
       </c>
       <c r="AC152" s="56"/>
     </row>
-    <row r="153" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="153" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A153" s="53">
         <v>211</v>
       </c>
@@ -35367,7 +35367,7 @@
       </c>
       <c r="AC153" s="56"/>
     </row>
-    <row r="154" spans="1:29" s="54" customFormat="1" ht="409.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="154" spans="1:29" s="54" customFormat="1" ht="409.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A154" s="53">
         <v>213</v>
       </c>
@@ -35458,7 +35458,7 @@
       </c>
       <c r="AC154" s="56"/>
     </row>
-    <row r="155" spans="1:29" s="54" customFormat="1" ht="306" x14ac:dyDescent="1.1000000000000001">
+    <row r="155" spans="1:29" s="54" customFormat="1" ht="306" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="B155" s="69" t="s">
         <v>26</v>
       </c>
@@ -35545,7 +35545,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="156" spans="1:29" s="54" customFormat="1" ht="382.5" x14ac:dyDescent="1.1000000000000001">
+    <row r="156" spans="1:29" s="54" customFormat="1" ht="382.5" hidden="1" x14ac:dyDescent="1.1000000000000001">
       <c r="B156" s="81" t="s">
         <v>26</v>
       </c>
@@ -35640,8 +35640,7 @@
   <autoFilter ref="B3:AB156" xr:uid="{F9A4741E-2134-4562-B632-CA537B03EF9D}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Torrefação"/>
-        <filter val="Torrefação, Moagem, Café Cru"/>
+        <filter val="Geral"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:AB156">
@@ -37140,47 +37139,47 @@
     <row r="1" spans="1:20" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="1:20" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="117" t="s">
         <v>211</v>
       </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="140"/>
+      <c r="C2" s="117"/>
+      <c r="D2" s="118"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="141" t="s">
+      <c r="F2" s="119" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
-      <c r="N2" s="142"/>
-      <c r="O2" s="142"/>
-      <c r="P2" s="142"/>
-      <c r="Q2" s="142"/>
-      <c r="R2" s="142"/>
-      <c r="S2" s="142"/>
-      <c r="T2" s="143"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
+      <c r="I2" s="120"/>
+      <c r="J2" s="120"/>
+      <c r="K2" s="120"/>
+      <c r="L2" s="120"/>
+      <c r="M2" s="120"/>
+      <c r="N2" s="120"/>
+      <c r="O2" s="120"/>
+      <c r="P2" s="120"/>
+      <c r="Q2" s="120"/>
+      <c r="R2" s="120"/>
+      <c r="S2" s="120"/>
+      <c r="T2" s="121"/>
     </row>
     <row r="3" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="123"/>
-      <c r="C3" s="123"/>
-      <c r="D3" s="123"/>
-      <c r="E3" s="123"/>
-      <c r="F3" s="123"/>
-      <c r="G3" s="123"/>
-      <c r="H3" s="123"/>
-      <c r="I3" s="123"/>
-      <c r="J3" s="123"/>
-      <c r="K3" s="123"/>
-      <c r="L3" s="123"/>
-      <c r="M3" s="123"/>
-      <c r="N3" s="123"/>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="123"/>
+      <c r="B3" s="122"/>
+      <c r="C3" s="122"/>
+      <c r="D3" s="122"/>
+      <c r="E3" s="122"/>
+      <c r="F3" s="122"/>
+      <c r="G3" s="122"/>
+      <c r="H3" s="122"/>
+      <c r="I3" s="122"/>
+      <c r="J3" s="122"/>
+      <c r="K3" s="122"/>
+      <c r="L3" s="122"/>
+      <c r="M3" s="122"/>
+      <c r="N3" s="122"/>
+      <c r="O3" s="122"/>
+      <c r="P3" s="122"/>
+      <c r="Q3" s="122"/>
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
@@ -37199,10 +37198,10 @@
       <c r="H4" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="144" t="s">
+      <c r="J4" s="123" t="s">
         <v>216</v>
       </c>
-      <c r="K4" s="145"/>
+      <c r="K4" s="124"/>
       <c r="M4" s="7">
         <f>IF(M18=6,H16,IF(M18=5,H14,IF(M18=4,H12,IF(M18=3,H10,IF(M18=2,H8,IF(M18=1,H6,""))))))</f>
         <v>10</v>
@@ -37585,27 +37584,27 @@
       <c r="T23" s="11"/>
     </row>
     <row r="24" spans="2:20" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="125" t="s">
         <v>243</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="148"/>
+      <c r="C24" s="126"/>
+      <c r="D24" s="127"/>
       <c r="F24" s="26" t="e">
         <f>(F4*M4)*S4</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H24" s="149" t="s">
+      <c r="H24" s="128" t="s">
         <v>244</v>
       </c>
-      <c r="I24" s="147"/>
-      <c r="J24" s="147"/>
-      <c r="K24" s="147"/>
-      <c r="L24" s="147"/>
-      <c r="M24" s="147"/>
-      <c r="N24" s="147"/>
-      <c r="O24" s="147"/>
-      <c r="P24" s="147"/>
-      <c r="Q24" s="148"/>
+      <c r="I24" s="126"/>
+      <c r="J24" s="126"/>
+      <c r="K24" s="126"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="126"/>
+      <c r="N24" s="126"/>
+      <c r="O24" s="126"/>
+      <c r="P24" s="126"/>
+      <c r="Q24" s="127"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
@@ -37616,27 +37615,27 @@
       <c r="D25" s="27"/>
     </row>
     <row r="26" spans="2:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B26" s="124" t="s">
+      <c r="B26" s="135" t="s">
         <v>245</v>
       </c>
-      <c r="C26" s="125"/>
-      <c r="D26" s="126"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="137"/>
       <c r="F26" s="28" t="e">
         <f>IF($F$24&gt;=400,"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H26" s="127" t="s">
+      <c r="H26" s="138" t="s">
         <v>246</v>
       </c>
-      <c r="I26" s="128"/>
-      <c r="J26" s="128"/>
-      <c r="K26" s="128"/>
-      <c r="L26" s="128"/>
-      <c r="M26" s="128"/>
-      <c r="N26" s="128"/>
-      <c r="O26" s="128"/>
-      <c r="P26" s="128"/>
-      <c r="Q26" s="129"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
+      <c r="L26" s="139"/>
+      <c r="M26" s="139"/>
+      <c r="N26" s="139"/>
+      <c r="O26" s="139"/>
+      <c r="P26" s="139"/>
+      <c r="Q26" s="140"/>
       <c r="R26" s="1"/>
       <c r="S26" s="28" t="e">
         <f>IF($F$24&gt;=400,"&lt;","")</f>
@@ -37664,23 +37663,23 @@
       <c r="T27" s="1"/>
     </row>
     <row r="28" spans="2:20" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="136" t="s">
+      <c r="B28" s="147" t="s">
         <v>247</v>
       </c>
-      <c r="C28" s="137"/>
-      <c r="D28" s="138"/>
-      <c r="H28" s="127" t="s">
+      <c r="C28" s="148"/>
+      <c r="D28" s="149"/>
+      <c r="H28" s="138" t="s">
         <v>248</v>
       </c>
-      <c r="I28" s="128"/>
-      <c r="J28" s="128"/>
-      <c r="K28" s="128"/>
-      <c r="L28" s="128"/>
-      <c r="M28" s="128"/>
-      <c r="N28" s="128"/>
-      <c r="O28" s="128"/>
-      <c r="P28" s="128"/>
-      <c r="Q28" s="129"/>
+      <c r="I28" s="139"/>
+      <c r="J28" s="139"/>
+      <c r="K28" s="139"/>
+      <c r="L28" s="139"/>
+      <c r="M28" s="139"/>
+      <c r="N28" s="139"/>
+      <c r="O28" s="139"/>
+      <c r="P28" s="139"/>
+      <c r="Q28" s="140"/>
     </row>
     <row r="29" spans="2:20" ht="5.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="27"/>
@@ -37698,27 +37697,27 @@
       <c r="Q29" s="27"/>
     </row>
     <row r="30" spans="2:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B30" s="130" t="s">
+      <c r="B30" s="141" t="s">
         <v>249</v>
       </c>
-      <c r="C30" s="131"/>
-      <c r="D30" s="132"/>
+      <c r="C30" s="142"/>
+      <c r="D30" s="143"/>
       <c r="F30" s="28" t="e">
         <f>IF(AND($F24&lt;400,$F$24&gt;=200),"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H30" s="120" t="s">
+      <c r="H30" s="132" t="s">
         <v>250</v>
       </c>
-      <c r="I30" s="121"/>
-      <c r="J30" s="121"/>
-      <c r="K30" s="121"/>
-      <c r="L30" s="121"/>
-      <c r="M30" s="121"/>
-      <c r="N30" s="121"/>
-      <c r="O30" s="121"/>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="122"/>
+      <c r="I30" s="133"/>
+      <c r="J30" s="133"/>
+      <c r="K30" s="133"/>
+      <c r="L30" s="133"/>
+      <c r="M30" s="133"/>
+      <c r="N30" s="133"/>
+      <c r="O30" s="133"/>
+      <c r="P30" s="133"/>
+      <c r="Q30" s="134"/>
       <c r="R30" s="1"/>
       <c r="S30" s="28" t="e">
         <f>IF(AND($F24&lt;400,$F$24&gt;=200),"&lt;","")</f>
@@ -37742,27 +37741,27 @@
       <c r="Q31" s="27"/>
     </row>
     <row r="32" spans="2:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B32" s="133" t="s">
+      <c r="B32" s="144" t="s">
         <v>251</v>
       </c>
-      <c r="C32" s="134"/>
-      <c r="D32" s="135"/>
+      <c r="C32" s="145"/>
+      <c r="D32" s="146"/>
       <c r="F32" s="28" t="e">
         <f>IF(AND($F$24&lt;200,$F$24&gt;=70),"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H32" s="120" t="s">
+      <c r="H32" s="132" t="s">
         <v>252</v>
       </c>
-      <c r="I32" s="121"/>
-      <c r="J32" s="121"/>
-      <c r="K32" s="121"/>
-      <c r="L32" s="121"/>
-      <c r="M32" s="121"/>
-      <c r="N32" s="121"/>
-      <c r="O32" s="121"/>
-      <c r="P32" s="121"/>
-      <c r="Q32" s="122"/>
+      <c r="I32" s="133"/>
+      <c r="J32" s="133"/>
+      <c r="K32" s="133"/>
+      <c r="L32" s="133"/>
+      <c r="M32" s="133"/>
+      <c r="N32" s="133"/>
+      <c r="O32" s="133"/>
+      <c r="P32" s="133"/>
+      <c r="Q32" s="134"/>
       <c r="R32" s="1"/>
       <c r="S32" s="28" t="e">
         <f>IF(AND($F$24&lt;200,$F$24&gt;=70),"&lt;","")</f>
@@ -37801,27 +37800,27 @@
       <c r="Q34" s="27"/>
     </row>
     <row r="35" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="B35" s="117" t="s">
+      <c r="B35" s="129" t="s">
         <v>253</v>
       </c>
-      <c r="C35" s="118"/>
-      <c r="D35" s="119"/>
+      <c r="C35" s="130"/>
+      <c r="D35" s="131"/>
       <c r="F35" s="28" t="e">
         <f>IF($F$24&lt;20,"&gt;","")</f>
         <v>#VALUE!</v>
       </c>
-      <c r="H35" s="120" t="s">
+      <c r="H35" s="132" t="s">
         <v>254</v>
       </c>
-      <c r="I35" s="121"/>
-      <c r="J35" s="121"/>
-      <c r="K35" s="121"/>
-      <c r="L35" s="121"/>
-      <c r="M35" s="121"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="121"/>
-      <c r="Q35" s="122"/>
+      <c r="I35" s="133"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="133"/>
+      <c r="M35" s="133"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="133"/>
+      <c r="P35" s="133"/>
+      <c r="Q35" s="134"/>
       <c r="R35" s="1"/>
       <c r="S35" s="28" t="e">
         <f>IF($F$24&lt;20,"&lt;","")</f>
@@ -37831,22 +37830,22 @@
     </row>
     <row r="36" spans="2:20" ht="5.15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="37" spans="2:20" ht="12.5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="123"/>
-      <c r="C37" s="123"/>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
-      <c r="G37" s="123"/>
-      <c r="H37" s="123"/>
-      <c r="I37" s="123"/>
-      <c r="J37" s="123"/>
-      <c r="K37" s="123"/>
-      <c r="L37" s="123"/>
-      <c r="M37" s="123"/>
-      <c r="N37" s="123"/>
-      <c r="O37" s="123"/>
-      <c r="P37" s="123"/>
-      <c r="Q37" s="123"/>
+      <c r="B37" s="122"/>
+      <c r="C37" s="122"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="122"/>
+      <c r="F37" s="122"/>
+      <c r="G37" s="122"/>
+      <c r="H37" s="122"/>
+      <c r="I37" s="122"/>
+      <c r="J37" s="122"/>
+      <c r="K37" s="122"/>
+      <c r="L37" s="122"/>
+      <c r="M37" s="122"/>
+      <c r="N37" s="122"/>
+      <c r="O37" s="122"/>
+      <c r="P37" s="122"/>
+      <c r="Q37" s="122"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
@@ -37866,12 +37865,6 @@
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <mergeCells count="17">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:T2"/>
-    <mergeCell ref="B3:Q3"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="H24:Q24"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="H35:Q35"/>
     <mergeCell ref="B37:Q37"/>
@@ -37883,6 +37876,12 @@
     <mergeCell ref="H32:Q32"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="H28:Q28"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:T2"/>
+    <mergeCell ref="B3:Q3"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="H24:Q24"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.9055118110236221" right="0.74803149606299213" top="0.74803149606299213" bottom="0.6692913385826772" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -39286,20 +39285,20 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="ee15a44e-0948-420d-96df-d16ce70ffded" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="ee15a44e-0948-420d-96df-d16ce70ffded" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -39322,6 +39321,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE14A1C-5FB1-4FE4-BBAD-C2D265A18624}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1FD52C5A-C1F0-4A58-ABE1-434C0069F4B0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="ee15a44e-0948-420d-96df-d16ce70ffded"/>
@@ -39336,12 +39343,4 @@
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE14A1C-5FB1-4FE4-BBAD-C2D265A18624}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>